--- a/MuoiCu_Server/templates/Phieu_Sua_Chua.xlsx
+++ b/MuoiCu_Server/templates/Phieu_Sua_Chua.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>Mã HEAD/Tên HEAD</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
   </si>
   <si>
     <t>Tên khách hàng: VÕ HOÀNG TRỌNG</t>
@@ -1619,16 +1616,14 @@
         <v>6</v>
       </c>
       <c r="AD6" s="30"/>
-      <c r="AE6" s="31" t="s">
-        <v>7</v>
-      </c>
+      <c r="AE6" s="31"/>
       <c r="AF6" s="15"/>
       <c r="AG6" s="15"/>
       <c r="AH6" s="2"/>
     </row>
     <row r="7" ht="28.5" customHeight="1">
       <c r="A7" s="32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="33"/>
       <c r="C7" s="33"/>
@@ -1639,7 +1634,7 @@
       <c r="H7" s="33"/>
       <c r="I7" s="34"/>
       <c r="J7" s="35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K7" s="33"/>
       <c r="L7" s="33"/>
@@ -1655,7 +1650,7 @@
       <c r="V7" s="33"/>
       <c r="W7" s="34"/>
       <c r="X7" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7" s="37"/>
       <c r="Z7" s="37"/>
@@ -1693,7 +1688,7 @@
       <c r="V8" s="44"/>
       <c r="W8" s="45"/>
       <c r="X8" s="36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y8" s="37"/>
       <c r="Z8" s="37"/>
@@ -1708,7 +1703,7 @@
     </row>
     <row r="9" ht="36.75" customHeight="1">
       <c r="A9" s="36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="47"/>
       <c r="C9" s="47"/>
@@ -1719,7 +1714,7 @@
       <c r="H9" s="47"/>
       <c r="I9" s="48"/>
       <c r="J9" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K9" s="29"/>
       <c r="L9" s="29"/>
@@ -1735,7 +1730,7 @@
       <c r="V9" s="29"/>
       <c r="W9" s="30"/>
       <c r="X9" s="36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y9" s="37"/>
       <c r="Z9" s="37"/>
@@ -1750,7 +1745,7 @@
     </row>
     <row r="10" ht="36.75" customHeight="1">
       <c r="A10" s="49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="50"/>
       <c r="C10" s="50"/>
@@ -1761,7 +1756,7 @@
       <c r="H10" s="51"/>
       <c r="I10" s="52"/>
       <c r="J10" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" s="29"/>
       <c r="L10" s="29"/>
@@ -1777,7 +1772,7 @@
       <c r="V10" s="29"/>
       <c r="W10" s="30"/>
       <c r="X10" s="53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y10" s="54"/>
       <c r="Z10" s="54"/>
@@ -1792,7 +1787,7 @@
     </row>
     <row r="11" ht="36.75" customHeight="1">
       <c r="A11" s="49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="47"/>
       <c r="C11" s="55"/>
@@ -1801,11 +1796,11 @@
       <c r="F11" s="55"/>
       <c r="G11" s="55"/>
       <c r="H11" s="51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I11" s="30"/>
       <c r="J11" s="36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K11" s="29"/>
       <c r="L11" s="29"/>
@@ -1821,7 +1816,7 @@
       <c r="V11" s="29"/>
       <c r="W11" s="30"/>
       <c r="X11" s="53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y11" s="54"/>
       <c r="Z11" s="54"/>
@@ -1836,7 +1831,7 @@
     </row>
     <row r="12" ht="26.25" customHeight="1">
       <c r="A12" s="56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="29"/>
       <c r="C12" s="29"/>
@@ -1848,7 +1843,7 @@
       <c r="I12" s="48"/>
       <c r="J12" s="57"/>
       <c r="K12" s="58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L12" s="29"/>
       <c r="M12" s="29"/>
@@ -1869,7 +1864,7 @@
       <c r="AB12" s="29"/>
       <c r="AC12" s="30"/>
       <c r="AD12" s="56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE12" s="30"/>
       <c r="AF12" s="15"/>
@@ -1878,7 +1873,7 @@
     </row>
     <row r="13" ht="34.5" customHeight="1">
       <c r="A13" s="59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="33"/>
       <c r="C13" s="33"/>
@@ -1889,7 +1884,7 @@
       <c r="H13" s="33"/>
       <c r="I13" s="34"/>
       <c r="J13" s="60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K13" s="33"/>
       <c r="L13" s="33"/>
@@ -1912,7 +1907,7 @@
       <c r="AC13" s="34"/>
       <c r="AD13" s="61"/>
       <c r="AE13" s="62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF13" s="15"/>
       <c r="AG13" s="15"/>
@@ -1925,7 +1920,7 @@
       <c r="AC14" s="64"/>
       <c r="AD14" s="61"/>
       <c r="AE14" s="65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF14" s="15"/>
       <c r="AG14" s="15"/>
@@ -1963,7 +1958,7 @@
       <c r="AC15" s="45"/>
       <c r="AD15" s="61"/>
       <c r="AE15" s="66" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF15" s="15"/>
       <c r="AG15" s="15"/>
@@ -2007,7 +2002,7 @@
     </row>
     <row r="17" ht="31.5" customHeight="1">
       <c r="A17" s="68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="29"/>
       <c r="C17" s="29"/>
@@ -2021,11 +2016,11 @@
       <c r="K17" s="29"/>
       <c r="L17" s="69"/>
       <c r="M17" s="70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N17" s="30"/>
       <c r="O17" s="71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P17" s="29"/>
       <c r="Q17" s="29"/>
@@ -2049,10 +2044,10 @@
     </row>
     <row r="18" ht="45.75" customHeight="1">
       <c r="A18" s="72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="73" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="29"/>
       <c r="D18" s="29"/>
@@ -2060,30 +2055,30 @@
       <c r="F18" s="29"/>
       <c r="G18" s="30"/>
       <c r="H18" s="73" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I18" s="30"/>
       <c r="J18" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="K18" s="75" t="s">
+      <c r="L18" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="L18" s="76" t="s">
+      <c r="M18" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="M18" s="77" t="s">
+      <c r="N18" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="77" t="s">
+      <c r="O18" s="73" t="s">
         <v>40</v>
-      </c>
-      <c r="O18" s="73" t="s">
-        <v>41</v>
       </c>
       <c r="P18" s="30"/>
       <c r="Q18" s="78" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R18" s="29"/>
       <c r="S18" s="29"/>
@@ -2093,14 +2088,14 @@
       <c r="W18" s="29"/>
       <c r="X18" s="30"/>
       <c r="Y18" s="78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z18" s="29"/>
       <c r="AA18" s="29"/>
       <c r="AB18" s="29"/>
       <c r="AC18" s="30"/>
       <c r="AD18" s="78" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AE18" s="30"/>
       <c r="AF18" s="2"/>
@@ -2112,7 +2107,7 @@
         <v>1.0</v>
       </c>
       <c r="B19" s="79" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="80"/>
       <c r="D19" s="80"/>
@@ -2120,7 +2115,7 @@
       <c r="F19" s="80"/>
       <c r="G19" s="81"/>
       <c r="H19" s="82" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I19" s="30"/>
       <c r="J19" s="82"/>
@@ -2846,7 +2841,7 @@
         <v>20.0</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" s="29"/>
       <c r="D38" s="29"/>
@@ -2961,7 +2956,7 @@
     </row>
     <row r="41" ht="24.0" customHeight="1">
       <c r="A41" s="103" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="104"/>
       <c r="C41" s="104"/>
@@ -2970,17 +2965,17 @@
       <c r="F41" s="104"/>
       <c r="G41" s="104"/>
       <c r="H41" s="105" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I41" s="106"/>
       <c r="J41" s="56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K41" s="29"/>
       <c r="L41" s="107"/>
       <c r="M41" s="108"/>
       <c r="N41" s="109" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O41" s="110"/>
       <c r="P41" s="110"/>
@@ -3018,7 +3013,7 @@
       <c r="L42" s="114"/>
       <c r="M42" s="114"/>
       <c r="N42" s="115" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O42" s="33"/>
       <c r="P42" s="33"/>
@@ -3034,12 +3029,12 @@
       <c r="Z42" s="33"/>
       <c r="AA42" s="34"/>
       <c r="AB42" s="116" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AC42" s="33"/>
       <c r="AD42" s="34"/>
       <c r="AE42" s="117" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AF42" s="2"/>
       <c r="AG42" s="2"/>
@@ -3047,7 +3042,7 @@
     </row>
     <row r="43" ht="19.5" customHeight="1">
       <c r="A43" s="118" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" s="27"/>
       <c r="C43" s="27"/>
@@ -3098,7 +3093,7 @@
       <c r="L44" s="124"/>
       <c r="M44" s="114"/>
       <c r="N44" s="125" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O44" s="33"/>
       <c r="P44" s="33"/>
@@ -3150,7 +3145,7 @@
     </row>
     <row r="46" ht="19.5" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3247,14 +3242,14 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="135"/>
       <c r="D49" s="135"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -3776,7 +3771,7 @@
     </row>
     <row r="65" ht="43.5" customHeight="1">
       <c r="A65" s="144" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AF65" s="2"/>
       <c r="AG65" s="2"/>

--- a/MuoiCu_Server/templates/Phieu_Sua_Chua.xlsx
+++ b/MuoiCu_Server/templates/Phieu_Sua_Chua.xlsx
@@ -1,25 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tt20363771\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC7E074-53F1-4524-9128-C920E934230D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Mẫu phiếu SC mới" sheetId="1" r:id="rId4"/>
+    <sheet name="Mẫu phiếu SC mới" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="B34">
+    <comment ref="B34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
-        <t xml:space="preserve">
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -50,12 +67,6 @@
     <t>E</t>
   </si>
   <si>
-    <t xml:space="preserve">Tên khách hàng: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Địa chỉ hiện tại: </t>
-  </si>
-  <si>
     <t xml:space="preserve">Thời gian nhận xe : </t>
   </si>
   <si>
@@ -79,19 +90,19 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
         <rFont val="Tahoma"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="14.0"/>
       </rPr>
       <t xml:space="preserve">ID Pin ( Xe điện ) : </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Tahoma"/>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <sz val="14.0"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -217,103 +228,144 @@
   <si>
     <r>
       <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
         <rFont val="Tahoma"/>
-        <color theme="1"/>
-        <sz val="14.0"/>
       </rPr>
       <t xml:space="preserve">Bằng việc ký vào Phiếu sửa chữa này, khách hàng đồng ý với Điều khoản và Chính Sách Quyền Riêng Tư. Trường hợp không đồng ý hoặc có ý kiến với mục đích xử lý dữ liệu cá nhân hoặc các nội dung khác tại Chính Sách Quyền Riêng tư, vui lòng liên hệ lại với chúng tôi qua hotline 1800.8001 Chi tiết chính sách quyền riêng tư, vui lòng truy cập tại: </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="14.0"/>
       </rPr>
       <t>www.honda.com/policy</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>Địa chỉ hiện tại:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Tên khách hàng:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color rgb="FFFF0000"/>
       <name val="Tahoma"/>
     </font>
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <b/>
-      <sz val="36.0"/>
+      <sz val="36"/>
       <color theme="1"/>
       <name val="Tahoma"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Tahoma"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="0"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="20.0"/>
+      <sz val="20"/>
       <color rgb="FF0000FF"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF0000FF"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Tahoma"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="0"/>
       <name val="Tahoma"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Tahoma"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -321,7 +373,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -373,11 +425,21 @@
     </fill>
   </fills>
   <borders count="39">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="dotted">
@@ -389,27 +451,35 @@
       <top style="dotted">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="dotted">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="dotted">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="dotted">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="dotted">
         <color rgb="FF000000"/>
       </right>
@@ -419,6 +489,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="dotted">
@@ -427,62 +498,82 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="dotted">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="dotted">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="dotted">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="dotted">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="dotted">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -492,6 +583,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -506,50 +598,72 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -559,8 +673,10 @@
       <bottom style="hair">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -570,8 +686,10 @@
       <bottom style="hair">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -581,8 +699,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -590,27 +710,34 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="hair">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="hair">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="hair">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="hair">
         <color rgb="FF000000"/>
       </right>
@@ -620,6 +747,7 @@
       <bottom style="hair">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -632,6 +760,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -642,6 +771,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -654,6 +784,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -662,28 +793,37 @@
       <right/>
       <top/>
       <bottom/>
-    </border>
-    <border>
-      <left/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -695,6 +835,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -703,9 +845,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -714,402 +858,416 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="148">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf quotePrefix="1" borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="5" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="19" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="20" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="0" fontId="5" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="19" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="18" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="21" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="22" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="18" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="11" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="24" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="5" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="6" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="27" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="28" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="29" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="30" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="31" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="32" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="34" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="28" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="29" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="35" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="36" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="35" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="37" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="5" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="38" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="35" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="36" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="36" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="19" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1117,47 +1275,44 @@
       <xdr:row>49</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="8715375" cy="3381375"/>
+    <xdr:ext cx="8870706" cy="3381375"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png"/>
+        <xdr:cNvPr id="2" name="image1.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{BEBA8EAE-BF5A-486C-A8C5-ECC9F3942E4B}">
+              <a14:imgProps xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a14:imgLayer r:embed="rId2">
+                  <a14:imgEffect>
+                    <a14:sharpenSoften amount="6000"/>
+                  </a14:imgEffect>
+                  <a14:imgEffect>
+                    <a14:brightnessContrast bright="-2000" contrast="-3000"/>
+                  </a14:imgEffect>
+                </a14:imgLayer>
+              </a14:imgProps>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="8715375" cy="3381375"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9525" y="19986869"/>
+          <a:ext cx="8870706" cy="3381375"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -1170,7 +1325,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1360,47 +1515,50 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:AH1000"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="1" min="1" max="5" width="5.86"/>
-    <col customWidth="1" min="6" max="6" width="6.43"/>
-    <col customWidth="1" min="7" max="7" width="9.71"/>
-    <col customWidth="1" min="8" max="8" width="25.71"/>
-    <col customWidth="1" min="9" max="9" width="18.43"/>
-    <col customWidth="1" min="10" max="10" width="12.14"/>
-    <col customWidth="1" min="11" max="11" width="9.86"/>
-    <col customWidth="1" min="12" max="12" width="19.43"/>
-    <col customWidth="1" min="13" max="13" width="7.86"/>
-    <col customWidth="1" min="14" max="14" width="11.0"/>
-    <col customWidth="1" min="15" max="15" width="6.43"/>
-    <col customWidth="1" min="16" max="16" width="2.86"/>
-    <col customWidth="1" min="17" max="17" width="6.43"/>
-    <col customWidth="1" min="18" max="18" width="8.14"/>
-    <col customWidth="1" min="19" max="19" width="5.43"/>
-    <col customWidth="1" min="20" max="21" width="2.86"/>
-    <col customWidth="1" min="22" max="22" width="3.43"/>
-    <col customWidth="1" min="23" max="23" width="2.86"/>
-    <col customWidth="1" min="24" max="24" width="5.43"/>
-    <col customWidth="1" min="25" max="25" width="3.43"/>
-    <col customWidth="1" min="26" max="26" width="3.0"/>
-    <col customWidth="1" hidden="1" min="27" max="27" width="2.0"/>
-    <col customWidth="1" min="28" max="28" width="6.71"/>
-    <col customWidth="1" min="29" max="29" width="9.86"/>
-    <col customWidth="1" min="30" max="30" width="9.71"/>
-    <col customWidth="1" min="31" max="31" width="30.14"/>
-    <col customWidth="1" min="32" max="34" width="9.14"/>
+    <col min="1" max="5" width="5.81640625" customWidth="1"/>
+    <col min="6" max="6" width="6.453125" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" customWidth="1"/>
+    <col min="8" max="8" width="25.7265625" customWidth="1"/>
+    <col min="9" max="9" width="18.453125" customWidth="1"/>
+    <col min="10" max="10" width="12.08984375" customWidth="1"/>
+    <col min="11" max="11" width="9.81640625" customWidth="1"/>
+    <col min="12" max="12" width="19.453125" customWidth="1"/>
+    <col min="13" max="13" width="7.81640625" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="6.453125" customWidth="1"/>
+    <col min="16" max="16" width="2.81640625" customWidth="1"/>
+    <col min="17" max="17" width="6.453125" customWidth="1"/>
+    <col min="18" max="18" width="8.08984375" customWidth="1"/>
+    <col min="19" max="19" width="5.453125" customWidth="1"/>
+    <col min="20" max="21" width="2.81640625" customWidth="1"/>
+    <col min="22" max="22" width="3.453125" customWidth="1"/>
+    <col min="23" max="23" width="2.81640625" customWidth="1"/>
+    <col min="24" max="24" width="5.453125" customWidth="1"/>
+    <col min="25" max="25" width="3.453125" customWidth="1"/>
+    <col min="26" max="26" width="3" customWidth="1"/>
+    <col min="27" max="27" width="2" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="10.08984375" customWidth="1"/>
+    <col min="29" max="29" width="9.81640625" customWidth="1"/>
+    <col min="30" max="30" width="9.7265625" customWidth="1"/>
+    <col min="31" max="31" width="30.08984375" customWidth="1"/>
+    <col min="32" max="34" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.75" customHeight="1">
+    <row r="1" spans="1:34" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1433,1421 +1591,1506 @@
       <c r="AB1" s="2"/>
       <c r="AC1" s="3"/>
       <c r="AD1" s="3"/>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="94" t="s">
         <v>1</v>
       </c>
       <c r="AF1" s="2"/>
       <c r="AG1" s="2"/>
       <c r="AH1" s="2"/>
     </row>
-    <row r="2" ht="33.0" customHeight="1">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:34" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="9" t="s">
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="12" t="s">
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="99"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="99"/>
+      <c r="U2" s="99"/>
+      <c r="V2" s="99"/>
+      <c r="W2" s="99"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="7"/>
+      <c r="AC2" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="AE2" s="13"/>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-    </row>
-    <row r="3" ht="33.0" customHeight="1">
-      <c r="A3" s="16">
-        <v>49010.0</v>
+      <c r="AD2" s="99"/>
+      <c r="AE2" s="95"/>
+      <c r="AF2" s="8"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+    </row>
+    <row r="3" spans="1:34" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="101">
+        <v>49010</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="19"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-      <c r="AB3" s="11"/>
-      <c r="AC3" s="15"/>
-      <c r="AD3" s="20"/>
-      <c r="AE3" s="21"/>
-      <c r="AF3" s="15"/>
-      <c r="AG3" s="15"/>
-      <c r="AH3" s="15"/>
-    </row>
-    <row r="4" ht="24.75" customHeight="1">
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
+      <c r="O3" s="99"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="99"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="99"/>
+      <c r="T3" s="99"/>
+      <c r="U3" s="99"/>
+      <c r="V3" s="99"/>
+      <c r="W3" s="99"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="12"/>
+      <c r="AE3" s="13"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+    </row>
+    <row r="4" spans="1:34" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="11"/>
-      <c r="AC4" s="11"/>
-      <c r="AD4" s="22"/>
-      <c r="AE4" s="23"/>
-      <c r="AF4" s="15"/>
-      <c r="AG4" s="15"/>
-      <c r="AH4" s="15"/>
-    </row>
-    <row r="5" ht="15.0" customHeight="1">
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="99"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="99"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="99"/>
+      <c r="S4" s="99"/>
+      <c r="T4" s="99"/>
+      <c r="U4" s="99"/>
+      <c r="V4" s="99"/>
+      <c r="W4" s="99"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="7"/>
+      <c r="AC4" s="7"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="15"/>
+      <c r="AF4" s="9"/>
+      <c r="AG4" s="9"/>
+      <c r="AH4" s="9"/>
+    </row>
+    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="24"/>
-      <c r="AD5" s="20"/>
-      <c r="AE5" s="25"/>
-      <c r="AF5" s="15"/>
-      <c r="AG5" s="15"/>
-      <c r="AH5" s="15"/>
-    </row>
-    <row r="6" ht="24.75" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="28" t="s">
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="99"/>
+      <c r="S5" s="99"/>
+      <c r="T5" s="99"/>
+      <c r="U5" s="99"/>
+      <c r="V5" s="99"/>
+      <c r="W5" s="99"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="6"/>
+      <c r="AA5" s="6"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="16"/>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="17"/>
+      <c r="AF5" s="9"/>
+      <c r="AG5" s="9"/>
+      <c r="AH5" s="9"/>
+    </row>
+    <row r="6" spans="1:34" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="18"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="29"/>
-      <c r="AC6" s="30" t="s">
+      <c r="Y6" s="89"/>
+      <c r="Z6" s="89"/>
+      <c r="AA6" s="89"/>
+      <c r="AB6" s="89"/>
+      <c r="AC6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="AD6" s="31"/>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="15"/>
-      <c r="AG6" s="15"/>
+      <c r="AD6" s="21"/>
+      <c r="AE6" s="22"/>
+      <c r="AF6" s="9"/>
+      <c r="AG6" s="9"/>
       <c r="AH6" s="2"/>
     </row>
-    <row r="7" ht="28.5" customHeight="1">
-      <c r="A7" s="33" t="s">
+    <row r="7" spans="1:34" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="145" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="146" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="104"/>
+      <c r="L7" s="104"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="104"/>
+      <c r="O7" s="104"/>
+      <c r="P7" s="104"/>
+      <c r="Q7" s="104"/>
+      <c r="R7" s="104"/>
+      <c r="S7" s="104"/>
+      <c r="T7" s="104"/>
+      <c r="U7" s="104"/>
+      <c r="V7" s="104"/>
+      <c r="W7" s="105"/>
+      <c r="X7" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="36" t="s">
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="25"/>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="25"/>
+      <c r="AE7" s="26"/>
+      <c r="AF7" s="9"/>
+      <c r="AG7" s="9"/>
+      <c r="AH7" s="9"/>
+    </row>
+    <row r="8" spans="1:34" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="106"/>
+      <c r="K8" s="107"/>
+      <c r="L8" s="107"/>
+      <c r="M8" s="107"/>
+      <c r="N8" s="107"/>
+      <c r="O8" s="107"/>
+      <c r="P8" s="107"/>
+      <c r="Q8" s="107"/>
+      <c r="R8" s="107"/>
+      <c r="S8" s="107"/>
+      <c r="T8" s="107"/>
+      <c r="U8" s="107"/>
+      <c r="V8" s="107"/>
+      <c r="W8" s="108"/>
+      <c r="X8" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="34"/>
-      <c r="U7" s="34"/>
-      <c r="V7" s="34"/>
-      <c r="W7" s="35"/>
-      <c r="X7" s="37" t="s">
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="9"/>
+      <c r="AG8" s="9"/>
+      <c r="AH8" s="9"/>
+    </row>
+    <row r="9" spans="1:34" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="39"/>
-      <c r="AB7" s="39"/>
-      <c r="AC7" s="39"/>
-      <c r="AD7" s="39"/>
-      <c r="AE7" s="40"/>
-      <c r="AF7" s="15"/>
-      <c r="AG7" s="15"/>
-      <c r="AH7" s="15"/>
-    </row>
-    <row r="8" ht="28.5" customHeight="1">
-      <c r="A8" s="41"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="45"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="45"/>
-      <c r="R8" s="45"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="45"/>
-      <c r="U8" s="45"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="46"/>
-      <c r="X8" s="37" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="Y8" s="38"/>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="39"/>
-      <c r="AB8" s="39"/>
-      <c r="AC8" s="39"/>
-      <c r="AD8" s="39"/>
-      <c r="AE8" s="47"/>
-      <c r="AF8" s="15"/>
-      <c r="AG8" s="15"/>
-      <c r="AH8" s="15"/>
-    </row>
-    <row r="9" ht="36.75" customHeight="1">
-      <c r="A9" s="48" t="s">
+      <c r="K9" s="89"/>
+      <c r="L9" s="89"/>
+      <c r="M9" s="89"/>
+      <c r="N9" s="89"/>
+      <c r="O9" s="89"/>
+      <c r="P9" s="89"/>
+      <c r="Q9" s="89"/>
+      <c r="R9" s="89"/>
+      <c r="S9" s="89"/>
+      <c r="T9" s="89"/>
+      <c r="U9" s="89"/>
+      <c r="V9" s="89"/>
+      <c r="W9" s="90"/>
+      <c r="X9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="37" t="s">
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="26"/>
+      <c r="AF9" s="9"/>
+      <c r="AG9" s="9"/>
+      <c r="AH9" s="9"/>
+    </row>
+    <row r="10" spans="1:34" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="37" t="s">
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="Y9" s="38"/>
-      <c r="Z9" s="38"/>
-      <c r="AA9" s="38"/>
-      <c r="AB9" s="38"/>
-      <c r="AC9" s="38"/>
-      <c r="AD9" s="38"/>
-      <c r="AE9" s="40"/>
-      <c r="AF9" s="15"/>
-      <c r="AG9" s="15"/>
-      <c r="AH9" s="15"/>
-    </row>
-    <row r="10" ht="36.75" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="K10" s="89"/>
+      <c r="L10" s="89"/>
+      <c r="M10" s="89"/>
+      <c r="N10" s="89"/>
+      <c r="O10" s="89"/>
+      <c r="P10" s="89"/>
+      <c r="Q10" s="89"/>
+      <c r="R10" s="89"/>
+      <c r="S10" s="89"/>
+      <c r="T10" s="89"/>
+      <c r="U10" s="89"/>
+      <c r="V10" s="89"/>
+      <c r="W10" s="90"/>
+      <c r="X10" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="37" t="s">
+      <c r="Y10" s="38"/>
+      <c r="Z10" s="38"/>
+      <c r="AA10" s="38"/>
+      <c r="AB10" s="38"/>
+      <c r="AC10" s="38"/>
+      <c r="AD10" s="38"/>
+      <c r="AE10" s="32"/>
+      <c r="AF10" s="9"/>
+      <c r="AG10" s="9"/>
+      <c r="AH10" s="9"/>
+    </row>
+    <row r="11" spans="1:34" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="51"/>
-      <c r="X10" s="56" t="s">
+      <c r="B11" s="31"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="Y10" s="57"/>
-      <c r="Z10" s="57"/>
-      <c r="AA10" s="57"/>
-      <c r="AB10" s="57"/>
-      <c r="AC10" s="57"/>
-      <c r="AD10" s="57"/>
-      <c r="AE10" s="50"/>
-      <c r="AF10" s="15"/>
-      <c r="AG10" s="15"/>
-      <c r="AH10" s="15"/>
-    </row>
-    <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="52" t="s">
+      <c r="I11" s="90"/>
+      <c r="J11" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="59" t="s">
+      <c r="K11" s="89"/>
+      <c r="L11" s="89"/>
+      <c r="M11" s="89"/>
+      <c r="N11" s="89"/>
+      <c r="O11" s="89"/>
+      <c r="P11" s="89"/>
+      <c r="Q11" s="89"/>
+      <c r="R11" s="89"/>
+      <c r="S11" s="89"/>
+      <c r="T11" s="89"/>
+      <c r="U11" s="89"/>
+      <c r="V11" s="89"/>
+      <c r="W11" s="90"/>
+      <c r="X11" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="51"/>
-      <c r="J11" s="37" t="s">
+      <c r="Y11" s="38"/>
+      <c r="Z11" s="38"/>
+      <c r="AA11" s="38"/>
+      <c r="AB11" s="38"/>
+      <c r="AC11" s="38"/>
+      <c r="AD11" s="38"/>
+      <c r="AE11" s="32"/>
+      <c r="AF11" s="9"/>
+      <c r="AG11" s="9"/>
+      <c r="AH11" s="9"/>
+    </row>
+    <row r="12" spans="1:34" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="51"/>
-      <c r="X11" s="56" t="s">
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="89"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="Y11" s="57"/>
-      <c r="Z11" s="57"/>
-      <c r="AA11" s="57"/>
-      <c r="AB11" s="57"/>
-      <c r="AC11" s="57"/>
-      <c r="AD11" s="57"/>
-      <c r="AE11" s="50"/>
-      <c r="AF11" s="15"/>
-      <c r="AG11" s="15"/>
-      <c r="AH11" s="15"/>
-    </row>
-    <row r="12" ht="26.25" customHeight="1">
-      <c r="A12" s="60" t="s">
+      <c r="L12" s="89"/>
+      <c r="M12" s="89"/>
+      <c r="N12" s="89"/>
+      <c r="O12" s="89"/>
+      <c r="P12" s="89"/>
+      <c r="Q12" s="89"/>
+      <c r="R12" s="89"/>
+      <c r="S12" s="89"/>
+      <c r="T12" s="89"/>
+      <c r="U12" s="89"/>
+      <c r="V12" s="89"/>
+      <c r="W12" s="89"/>
+      <c r="X12" s="89"/>
+      <c r="Y12" s="89"/>
+      <c r="Z12" s="89"/>
+      <c r="AA12" s="89"/>
+      <c r="AB12" s="89"/>
+      <c r="AC12" s="90"/>
+      <c r="AD12" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="61" t="s">
+      <c r="AE12" s="90"/>
+      <c r="AF12" s="9"/>
+      <c r="AG12" s="9"/>
+      <c r="AH12" s="9"/>
+    </row>
+    <row r="13" spans="1:34" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="123"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="104"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="113"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="104"/>
+      <c r="O13" s="104"/>
+      <c r="P13" s="104"/>
+      <c r="Q13" s="104"/>
+      <c r="R13" s="104"/>
+      <c r="S13" s="104"/>
+      <c r="T13" s="104"/>
+      <c r="U13" s="104"/>
+      <c r="V13" s="104"/>
+      <c r="W13" s="104"/>
+      <c r="X13" s="104"/>
+      <c r="Y13" s="104"/>
+      <c r="Z13" s="104"/>
+      <c r="AA13" s="104"/>
+      <c r="AB13" s="104"/>
+      <c r="AC13" s="105"/>
+      <c r="AD13" s="40"/>
+      <c r="AE13" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="29"/>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="29"/>
-      <c r="AB12" s="29"/>
-      <c r="AC12" s="51"/>
-      <c r="AD12" s="60" t="s">
+      <c r="AF13" s="9"/>
+      <c r="AG13" s="9"/>
+      <c r="AH13" s="9"/>
+    </row>
+    <row r="14" spans="1:34" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="114"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="99"/>
+      <c r="L14" s="99"/>
+      <c r="M14" s="99"/>
+      <c r="N14" s="99"/>
+      <c r="O14" s="99"/>
+      <c r="P14" s="99"/>
+      <c r="Q14" s="99"/>
+      <c r="R14" s="99"/>
+      <c r="S14" s="99"/>
+      <c r="T14" s="99"/>
+      <c r="U14" s="99"/>
+      <c r="V14" s="99"/>
+      <c r="W14" s="99"/>
+      <c r="X14" s="99"/>
+      <c r="Y14" s="99"/>
+      <c r="Z14" s="99"/>
+      <c r="AA14" s="99"/>
+      <c r="AB14" s="99"/>
+      <c r="AC14" s="115"/>
+      <c r="AD14" s="40"/>
+      <c r="AE14" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="AE12" s="51"/>
-      <c r="AF12" s="15"/>
-      <c r="AG12" s="15"/>
-      <c r="AH12" s="15"/>
-    </row>
-    <row r="13" ht="34.5" customHeight="1">
-      <c r="A13" s="62"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="63"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="34"/>
-      <c r="W13" s="34"/>
-      <c r="X13" s="34"/>
-      <c r="Y13" s="34"/>
-      <c r="Z13" s="34"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="34"/>
-      <c r="AC13" s="35"/>
-      <c r="AD13" s="64"/>
-      <c r="AE13" s="65" t="s">
+      <c r="AF14" s="9"/>
+      <c r="AG14" s="9"/>
+      <c r="AH14" s="9"/>
+    </row>
+    <row r="15" spans="1:34" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="106"/>
+      <c r="B15" s="107"/>
+      <c r="C15" s="107"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="107"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="107"/>
+      <c r="L15" s="107"/>
+      <c r="M15" s="107"/>
+      <c r="N15" s="107"/>
+      <c r="O15" s="107"/>
+      <c r="P15" s="107"/>
+      <c r="Q15" s="107"/>
+      <c r="R15" s="107"/>
+      <c r="S15" s="107"/>
+      <c r="T15" s="107"/>
+      <c r="U15" s="107"/>
+      <c r="V15" s="107"/>
+      <c r="W15" s="107"/>
+      <c r="X15" s="107"/>
+      <c r="Y15" s="107"/>
+      <c r="Z15" s="107"/>
+      <c r="AA15" s="107"/>
+      <c r="AB15" s="107"/>
+      <c r="AC15" s="108"/>
+      <c r="AD15" s="40"/>
+      <c r="AE15" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="AF13" s="15"/>
-      <c r="AG13" s="15"/>
-      <c r="AH13" s="15"/>
-    </row>
-    <row r="14" ht="34.5" customHeight="1">
-      <c r="A14" s="66"/>
-      <c r="I14" s="67"/>
-      <c r="J14" s="66"/>
-      <c r="AC14" s="67"/>
-      <c r="AD14" s="64"/>
-      <c r="AE14" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF14" s="15"/>
-      <c r="AG14" s="15"/>
-      <c r="AH14" s="15"/>
-    </row>
-    <row r="15" ht="34.5" customHeight="1">
-      <c r="A15" s="44"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="45"/>
-      <c r="U15" s="45"/>
-      <c r="V15" s="45"/>
-      <c r="W15" s="45"/>
-      <c r="X15" s="45"/>
-      <c r="Y15" s="45"/>
-      <c r="Z15" s="45"/>
-      <c r="AA15" s="45"/>
-      <c r="AB15" s="45"/>
-      <c r="AC15" s="46"/>
-      <c r="AD15" s="64"/>
-      <c r="AE15" s="69" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF15" s="15"/>
-      <c r="AG15" s="15"/>
-      <c r="AH15" s="15"/>
-    </row>
-    <row r="16" ht="3.0" customHeight="1">
-      <c r="A16" s="70"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="45"/>
-      <c r="U16" s="45"/>
-      <c r="V16" s="45"/>
-      <c r="W16" s="45"/>
-      <c r="X16" s="45"/>
-      <c r="Y16" s="45"/>
-      <c r="Z16" s="45"/>
-      <c r="AA16" s="45"/>
-      <c r="AB16" s="45"/>
-      <c r="AC16" s="45"/>
-      <c r="AD16" s="45"/>
-      <c r="AE16" s="46"/>
+      <c r="AF15" s="9"/>
+      <c r="AG15" s="9"/>
+      <c r="AH15" s="9"/>
+    </row>
+    <row r="16" spans="1:34" ht="3" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="116"/>
+      <c r="B16" s="107"/>
+      <c r="C16" s="107"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="107"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="107"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="107"/>
+      <c r="L16" s="107"/>
+      <c r="M16" s="107"/>
+      <c r="N16" s="107"/>
+      <c r="O16" s="107"/>
+      <c r="P16" s="107"/>
+      <c r="Q16" s="107"/>
+      <c r="R16" s="107"/>
+      <c r="S16" s="107"/>
+      <c r="T16" s="107"/>
+      <c r="U16" s="107"/>
+      <c r="V16" s="107"/>
+      <c r="W16" s="107"/>
+      <c r="X16" s="107"/>
+      <c r="Y16" s="107"/>
+      <c r="Z16" s="107"/>
+      <c r="AA16" s="107"/>
+      <c r="AB16" s="107"/>
+      <c r="AC16" s="107"/>
+      <c r="AD16" s="107"/>
+      <c r="AE16" s="108"/>
       <c r="AF16" s="2"/>
       <c r="AG16" s="2"/>
       <c r="AH16" s="2"/>
     </row>
-    <row r="17" ht="31.5" customHeight="1">
-      <c r="A17" s="71" t="s">
+    <row r="17" spans="1:34" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="89"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="118"/>
+      <c r="M17" s="119" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="90"/>
+      <c r="O17" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="72"/>
-      <c r="M17" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="N17" s="51"/>
-      <c r="O17" s="74" t="s">
-        <v>29</v>
-      </c>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="29"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="29"/>
-      <c r="V17" s="29"/>
-      <c r="W17" s="29"/>
-      <c r="X17" s="29"/>
-      <c r="Y17" s="29"/>
-      <c r="Z17" s="29"/>
-      <c r="AA17" s="29"/>
-      <c r="AB17" s="29"/>
-      <c r="AC17" s="29"/>
-      <c r="AD17" s="29"/>
-      <c r="AE17" s="51"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="90"/>
       <c r="AF17" s="2"/>
       <c r="AG17" s="2"/>
       <c r="AH17" s="2"/>
     </row>
-    <row r="18" ht="45.75" customHeight="1">
-      <c r="A18" s="75" t="s">
+    <row r="18" spans="1:34" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="121" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="121" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="76" t="s">
+      <c r="I18" s="90"/>
+      <c r="J18" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="76" t="s">
+      <c r="K18" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="51"/>
-      <c r="J18" s="77" t="s">
+      <c r="L18" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="K18" s="78" t="s">
+      <c r="M18" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="L18" s="79" t="s">
+      <c r="N18" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="M18" s="80" t="s">
+      <c r="O18" s="121" t="s">
         <v>36</v>
       </c>
-      <c r="N18" s="80" t="s">
+      <c r="P18" s="90"/>
+      <c r="Q18" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="O18" s="76" t="s">
+      <c r="R18" s="89"/>
+      <c r="S18" s="89"/>
+      <c r="T18" s="89"/>
+      <c r="U18" s="89"/>
+      <c r="V18" s="89"/>
+      <c r="W18" s="89"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="81" t="s">
+      <c r="Z18" s="89"/>
+      <c r="AA18" s="89"/>
+      <c r="AB18" s="89"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="51"/>
-      <c r="Y18" s="81" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z18" s="29"/>
-      <c r="AA18" s="29"/>
-      <c r="AB18" s="29"/>
-      <c r="AC18" s="51"/>
-      <c r="AD18" s="81" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE18" s="51"/>
+      <c r="AE18" s="90"/>
       <c r="AF18" s="2"/>
       <c r="AG18" s="2"/>
       <c r="AH18" s="2"/>
     </row>
-    <row r="19" ht="43.5" customHeight="1">
-      <c r="A19" s="64">
-        <v>1.0</v>
+    <row r="19" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="40">
+        <v>1</v>
       </c>
-      <c r="B19" s="82"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="84"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="85"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="87"/>
-      <c r="M19" s="85"/>
-      <c r="N19" s="86"/>
+      <c r="B19" s="124"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="49"/>
+      <c r="N19" s="50"/>
       <c r="O19" s="88"/>
-      <c r="P19" s="51"/>
+      <c r="P19" s="90"/>
       <c r="Q19" s="88"/>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-      <c r="W19" s="29"/>
-      <c r="X19" s="51"/>
+      <c r="R19" s="89"/>
+      <c r="S19" s="89"/>
+      <c r="T19" s="89"/>
+      <c r="U19" s="89"/>
+      <c r="V19" s="89"/>
+      <c r="W19" s="89"/>
+      <c r="X19" s="90"/>
       <c r="Y19" s="88"/>
-      <c r="Z19" s="29"/>
-      <c r="AA19" s="29"/>
-      <c r="AB19" s="29"/>
-      <c r="AC19" s="51"/>
-      <c r="AD19" s="89"/>
-      <c r="AE19" s="51"/>
+      <c r="Z19" s="89"/>
+      <c r="AA19" s="89"/>
+      <c r="AB19" s="89"/>
+      <c r="AC19" s="90"/>
+      <c r="AD19" s="91"/>
+      <c r="AE19" s="90"/>
       <c r="AF19" s="2"/>
       <c r="AG19" s="2"/>
       <c r="AH19" s="2"/>
     </row>
-    <row r="20" ht="43.5" customHeight="1">
-      <c r="A20" s="64">
-        <v>2.0</v>
+    <row r="20" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="40">
+        <v>2</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="85"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="87"/>
-      <c r="M20" s="85"/>
-      <c r="N20" s="86"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="49"/>
+      <c r="N20" s="50"/>
       <c r="O20" s="88"/>
-      <c r="P20" s="51"/>
+      <c r="P20" s="90"/>
       <c r="Q20" s="88"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="51"/>
+      <c r="R20" s="89"/>
+      <c r="S20" s="89"/>
+      <c r="T20" s="89"/>
+      <c r="U20" s="89"/>
+      <c r="V20" s="89"/>
+      <c r="W20" s="89"/>
+      <c r="X20" s="90"/>
       <c r="Y20" s="88"/>
-      <c r="Z20" s="29"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="29"/>
-      <c r="AC20" s="51"/>
-      <c r="AD20" s="89"/>
-      <c r="AE20" s="51"/>
+      <c r="Z20" s="89"/>
+      <c r="AA20" s="89"/>
+      <c r="AB20" s="89"/>
+      <c r="AC20" s="90"/>
+      <c r="AD20" s="91"/>
+      <c r="AE20" s="90"/>
       <c r="AF20" s="2"/>
       <c r="AG20" s="2"/>
       <c r="AH20" s="2"/>
     </row>
-    <row r="21" ht="43.5" customHeight="1">
-      <c r="A21" s="64">
-        <v>3.0</v>
+    <row r="21" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="40">
+        <v>3</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="85"/>
-      <c r="K21" s="86"/>
-      <c r="L21" s="87"/>
-      <c r="M21" s="85"/>
-      <c r="N21" s="64"/>
+      <c r="B21" s="92"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="93"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="40"/>
       <c r="O21" s="88"/>
-      <c r="P21" s="51"/>
+      <c r="P21" s="90"/>
       <c r="Q21" s="88"/>
-      <c r="R21" s="29"/>
-      <c r="S21" s="29"/>
-      <c r="T21" s="29"/>
-      <c r="U21" s="29"/>
-      <c r="V21" s="29"/>
-      <c r="W21" s="29"/>
-      <c r="X21" s="51"/>
+      <c r="R21" s="89"/>
+      <c r="S21" s="89"/>
+      <c r="T21" s="89"/>
+      <c r="U21" s="89"/>
+      <c r="V21" s="89"/>
+      <c r="W21" s="89"/>
+      <c r="X21" s="90"/>
       <c r="Y21" s="88"/>
-      <c r="Z21" s="29"/>
-      <c r="AA21" s="29"/>
-      <c r="AB21" s="29"/>
-      <c r="AC21" s="51"/>
-      <c r="AD21" s="89"/>
-      <c r="AE21" s="51"/>
+      <c r="Z21" s="89"/>
+      <c r="AA21" s="89"/>
+      <c r="AB21" s="89"/>
+      <c r="AC21" s="90"/>
+      <c r="AD21" s="91"/>
+      <c r="AE21" s="90"/>
       <c r="AF21" s="2"/>
       <c r="AG21" s="2"/>
       <c r="AH21" s="2"/>
     </row>
-    <row r="22" ht="43.5" customHeight="1">
-      <c r="A22" s="64">
-        <v>4.0</v>
+    <row r="22" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="40">
+        <v>4</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="85"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="85"/>
-      <c r="K22" s="86"/>
-      <c r="L22" s="87"/>
-      <c r="M22" s="85"/>
-      <c r="N22" s="64"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="49"/>
+      <c r="N22" s="40"/>
       <c r="O22" s="88"/>
-      <c r="P22" s="51"/>
+      <c r="P22" s="90"/>
       <c r="Q22" s="88"/>
-      <c r="R22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="29"/>
-      <c r="W22" s="29"/>
-      <c r="X22" s="51"/>
+      <c r="R22" s="89"/>
+      <c r="S22" s="89"/>
+      <c r="T22" s="89"/>
+      <c r="U22" s="89"/>
+      <c r="V22" s="89"/>
+      <c r="W22" s="89"/>
+      <c r="X22" s="90"/>
       <c r="Y22" s="88"/>
-      <c r="Z22" s="29"/>
-      <c r="AA22" s="29"/>
-      <c r="AB22" s="29"/>
-      <c r="AC22" s="51"/>
-      <c r="AD22" s="89"/>
-      <c r="AE22" s="51"/>
+      <c r="Z22" s="89"/>
+      <c r="AA22" s="89"/>
+      <c r="AB22" s="89"/>
+      <c r="AC22" s="90"/>
+      <c r="AD22" s="91"/>
+      <c r="AE22" s="90"/>
       <c r="AF22" s="2"/>
       <c r="AG22" s="2"/>
       <c r="AH22" s="2"/>
     </row>
-    <row r="23" ht="43.5" customHeight="1">
-      <c r="A23" s="64">
-        <v>5.0</v>
+    <row r="23" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="40">
+        <v>5</v>
       </c>
-      <c r="B23" s="90"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="85"/>
-      <c r="K23" s="86"/>
-      <c r="L23" s="87"/>
-      <c r="M23" s="85"/>
-      <c r="N23" s="32"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="51"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="22"/>
       <c r="O23" s="88"/>
-      <c r="P23" s="51"/>
+      <c r="P23" s="90"/>
       <c r="Q23" s="88"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="51"/>
+      <c r="R23" s="89"/>
+      <c r="S23" s="89"/>
+      <c r="T23" s="89"/>
+      <c r="U23" s="89"/>
+      <c r="V23" s="89"/>
+      <c r="W23" s="89"/>
+      <c r="X23" s="90"/>
       <c r="Y23" s="88"/>
-      <c r="Z23" s="29"/>
-      <c r="AA23" s="29"/>
-      <c r="AB23" s="29"/>
-      <c r="AC23" s="51"/>
-      <c r="AD23" s="89"/>
-      <c r="AE23" s="51"/>
+      <c r="Z23" s="89"/>
+      <c r="AA23" s="89"/>
+      <c r="AB23" s="89"/>
+      <c r="AC23" s="90"/>
+      <c r="AD23" s="91"/>
+      <c r="AE23" s="90"/>
       <c r="AF23" s="2"/>
       <c r="AG23" s="2"/>
       <c r="AH23" s="2"/>
     </row>
-    <row r="24" ht="43.5" customHeight="1">
-      <c r="A24" s="64">
-        <v>6.0</v>
+    <row r="24" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="40">
+        <v>6</v>
       </c>
-      <c r="B24" s="90"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="85"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="85"/>
-      <c r="K24" s="86"/>
-      <c r="L24" s="87"/>
-      <c r="M24" s="85"/>
-      <c r="N24" s="32"/>
+      <c r="B24" s="92"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="22"/>
       <c r="O24" s="88"/>
-      <c r="P24" s="51"/>
+      <c r="P24" s="90"/>
       <c r="Q24" s="88"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-      <c r="W24" s="29"/>
-      <c r="X24" s="51"/>
+      <c r="R24" s="89"/>
+      <c r="S24" s="89"/>
+      <c r="T24" s="89"/>
+      <c r="U24" s="89"/>
+      <c r="V24" s="89"/>
+      <c r="W24" s="89"/>
+      <c r="X24" s="90"/>
       <c r="Y24" s="88"/>
-      <c r="Z24" s="29"/>
-      <c r="AA24" s="29"/>
-      <c r="AB24" s="29"/>
-      <c r="AC24" s="51"/>
-      <c r="AD24" s="89"/>
-      <c r="AE24" s="51"/>
+      <c r="Z24" s="89"/>
+      <c r="AA24" s="89"/>
+      <c r="AB24" s="89"/>
+      <c r="AC24" s="90"/>
+      <c r="AD24" s="91"/>
+      <c r="AE24" s="90"/>
       <c r="AF24" s="2"/>
       <c r="AG24" s="2"/>
       <c r="AH24" s="2"/>
     </row>
-    <row r="25" ht="43.5" customHeight="1">
-      <c r="A25" s="64">
-        <v>7.0</v>
+    <row r="25" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="40">
+        <v>7</v>
       </c>
-      <c r="B25" s="90"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="85"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="87"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="32"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="49"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="51"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="22"/>
       <c r="O25" s="88"/>
-      <c r="P25" s="51"/>
+      <c r="P25" s="90"/>
       <c r="Q25" s="88"/>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="29"/>
-      <c r="V25" s="29"/>
-      <c r="W25" s="29"/>
-      <c r="X25" s="51"/>
+      <c r="R25" s="89"/>
+      <c r="S25" s="89"/>
+      <c r="T25" s="89"/>
+      <c r="U25" s="89"/>
+      <c r="V25" s="89"/>
+      <c r="W25" s="89"/>
+      <c r="X25" s="90"/>
       <c r="Y25" s="88"/>
-      <c r="Z25" s="29"/>
-      <c r="AA25" s="29"/>
-      <c r="AB25" s="29"/>
-      <c r="AC25" s="51"/>
-      <c r="AD25" s="89"/>
-      <c r="AE25" s="51"/>
+      <c r="Z25" s="89"/>
+      <c r="AA25" s="89"/>
+      <c r="AB25" s="89"/>
+      <c r="AC25" s="90"/>
+      <c r="AD25" s="91"/>
+      <c r="AE25" s="90"/>
       <c r="AF25" s="2"/>
       <c r="AG25" s="2"/>
       <c r="AH25" s="2"/>
     </row>
-    <row r="26" ht="43.5" customHeight="1">
-      <c r="A26" s="64">
-        <v>8.0</v>
+    <row r="26" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="40">
+        <v>8</v>
       </c>
-      <c r="B26" s="90"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="32"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="90"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="51"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="22"/>
       <c r="O26" s="88"/>
-      <c r="P26" s="51"/>
+      <c r="P26" s="90"/>
       <c r="Q26" s="88"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="51"/>
+      <c r="R26" s="89"/>
+      <c r="S26" s="89"/>
+      <c r="T26" s="89"/>
+      <c r="U26" s="89"/>
+      <c r="V26" s="89"/>
+      <c r="W26" s="89"/>
+      <c r="X26" s="90"/>
       <c r="Y26" s="88"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="51"/>
-      <c r="AD26" s="89"/>
-      <c r="AE26" s="51"/>
+      <c r="Z26" s="89"/>
+      <c r="AA26" s="89"/>
+      <c r="AB26" s="89"/>
+      <c r="AC26" s="90"/>
+      <c r="AD26" s="91"/>
+      <c r="AE26" s="90"/>
       <c r="AF26" s="2"/>
       <c r="AG26" s="2"/>
       <c r="AH26" s="2"/>
     </row>
-    <row r="27" ht="43.5" customHeight="1">
-      <c r="A27" s="64">
-        <v>9.0</v>
+    <row r="27" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="40">
+        <v>9</v>
       </c>
-      <c r="B27" s="90"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="85"/>
-      <c r="N27" s="32"/>
+      <c r="B27" s="92"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="90"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="51"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="22"/>
       <c r="O27" s="88"/>
-      <c r="P27" s="51"/>
+      <c r="P27" s="90"/>
       <c r="Q27" s="88"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="29"/>
-      <c r="X27" s="51"/>
+      <c r="R27" s="89"/>
+      <c r="S27" s="89"/>
+      <c r="T27" s="89"/>
+      <c r="U27" s="89"/>
+      <c r="V27" s="89"/>
+      <c r="W27" s="89"/>
+      <c r="X27" s="90"/>
       <c r="Y27" s="88"/>
-      <c r="Z27" s="29"/>
-      <c r="AA27" s="29"/>
-      <c r="AB27" s="29"/>
-      <c r="AC27" s="51"/>
-      <c r="AD27" s="89"/>
-      <c r="AE27" s="51"/>
+      <c r="Z27" s="89"/>
+      <c r="AA27" s="89"/>
+      <c r="AB27" s="89"/>
+      <c r="AC27" s="90"/>
+      <c r="AD27" s="91"/>
+      <c r="AE27" s="90"/>
       <c r="AF27" s="2"/>
       <c r="AG27" s="2"/>
       <c r="AH27" s="2"/>
     </row>
-    <row r="28" ht="43.5" customHeight="1">
-      <c r="A28" s="64">
-        <v>10.0</v>
+    <row r="28" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="40">
+        <v>10</v>
       </c>
-      <c r="B28" s="90"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="85"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="85"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="87"/>
-      <c r="M28" s="85"/>
-      <c r="N28" s="32"/>
+      <c r="B28" s="92"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="51"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="22"/>
       <c r="O28" s="88"/>
-      <c r="P28" s="51"/>
+      <c r="P28" s="90"/>
       <c r="Q28" s="88"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-      <c r="W28" s="29"/>
-      <c r="X28" s="51"/>
+      <c r="R28" s="89"/>
+      <c r="S28" s="89"/>
+      <c r="T28" s="89"/>
+      <c r="U28" s="89"/>
+      <c r="V28" s="89"/>
+      <c r="W28" s="89"/>
+      <c r="X28" s="90"/>
       <c r="Y28" s="88"/>
-      <c r="Z28" s="29"/>
-      <c r="AA28" s="29"/>
-      <c r="AB28" s="29"/>
-      <c r="AC28" s="51"/>
-      <c r="AD28" s="89"/>
-      <c r="AE28" s="51"/>
+      <c r="Z28" s="89"/>
+      <c r="AA28" s="89"/>
+      <c r="AB28" s="89"/>
+      <c r="AC28" s="90"/>
+      <c r="AD28" s="91"/>
+      <c r="AE28" s="90"/>
       <c r="AF28" s="2"/>
       <c r="AG28" s="2"/>
       <c r="AH28" s="2"/>
     </row>
-    <row r="29" ht="43.5" customHeight="1">
-      <c r="A29" s="64">
-        <v>11.0</v>
+    <row r="29" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="40">
+        <v>11</v>
       </c>
-      <c r="B29" s="90"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="86"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="32"/>
+      <c r="B29" s="92"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="51"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="22"/>
       <c r="O29" s="88"/>
-      <c r="P29" s="51"/>
+      <c r="P29" s="90"/>
       <c r="Q29" s="88"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="51"/>
+      <c r="R29" s="89"/>
+      <c r="S29" s="89"/>
+      <c r="T29" s="89"/>
+      <c r="U29" s="89"/>
+      <c r="V29" s="89"/>
+      <c r="W29" s="89"/>
+      <c r="X29" s="90"/>
       <c r="Y29" s="88"/>
-      <c r="Z29" s="29"/>
-      <c r="AA29" s="29"/>
-      <c r="AB29" s="29"/>
-      <c r="AC29" s="51"/>
-      <c r="AD29" s="89"/>
-      <c r="AE29" s="51"/>
+      <c r="Z29" s="89"/>
+      <c r="AA29" s="89"/>
+      <c r="AB29" s="89"/>
+      <c r="AC29" s="90"/>
+      <c r="AD29" s="91"/>
+      <c r="AE29" s="90"/>
       <c r="AF29" s="2"/>
       <c r="AG29" s="2"/>
       <c r="AH29" s="2"/>
     </row>
-    <row r="30" ht="43.5" customHeight="1">
-      <c r="A30" s="64">
-        <v>12.0</v>
+    <row r="30" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="40">
+        <v>12</v>
       </c>
-      <c r="B30" s="90"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="32"/>
+      <c r="B30" s="92"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="51"/>
+      <c r="M30" s="49"/>
+      <c r="N30" s="22"/>
       <c r="O30" s="88"/>
-      <c r="P30" s="51"/>
+      <c r="P30" s="90"/>
       <c r="Q30" s="88"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="29"/>
-      <c r="T30" s="29"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="29"/>
-      <c r="W30" s="29"/>
-      <c r="X30" s="51"/>
+      <c r="R30" s="89"/>
+      <c r="S30" s="89"/>
+      <c r="T30" s="89"/>
+      <c r="U30" s="89"/>
+      <c r="V30" s="89"/>
+      <c r="W30" s="89"/>
+      <c r="X30" s="90"/>
       <c r="Y30" s="88"/>
-      <c r="Z30" s="29"/>
-      <c r="AA30" s="29"/>
-      <c r="AB30" s="29"/>
-      <c r="AC30" s="51"/>
-      <c r="AD30" s="89"/>
-      <c r="AE30" s="51"/>
+      <c r="Z30" s="89"/>
+      <c r="AA30" s="89"/>
+      <c r="AB30" s="89"/>
+      <c r="AC30" s="90"/>
+      <c r="AD30" s="91"/>
+      <c r="AE30" s="90"/>
       <c r="AF30" s="2"/>
       <c r="AG30" s="2"/>
       <c r="AH30" s="2"/>
     </row>
-    <row r="31" ht="43.5" customHeight="1">
-      <c r="A31" s="64">
-        <v>13.0</v>
+    <row r="31" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="40">
+        <v>13</v>
       </c>
-      <c r="B31" s="90"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="64"/>
-      <c r="K31" s="86"/>
-      <c r="L31" s="87"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="32"/>
+      <c r="B31" s="92"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="89"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="51"/>
+      <c r="M31" s="49"/>
+      <c r="N31" s="22"/>
       <c r="O31" s="88"/>
-      <c r="P31" s="51"/>
+      <c r="P31" s="90"/>
       <c r="Q31" s="88"/>
-      <c r="R31" s="29"/>
-      <c r="S31" s="29"/>
-      <c r="T31" s="29"/>
-      <c r="U31" s="29"/>
-      <c r="V31" s="29"/>
-      <c r="W31" s="29"/>
-      <c r="X31" s="51"/>
+      <c r="R31" s="89"/>
+      <c r="S31" s="89"/>
+      <c r="T31" s="89"/>
+      <c r="U31" s="89"/>
+      <c r="V31" s="89"/>
+      <c r="W31" s="89"/>
+      <c r="X31" s="90"/>
       <c r="Y31" s="88"/>
-      <c r="Z31" s="29"/>
-      <c r="AA31" s="29"/>
-      <c r="AB31" s="29"/>
-      <c r="AC31" s="51"/>
-      <c r="AD31" s="89"/>
-      <c r="AE31" s="51"/>
+      <c r="Z31" s="89"/>
+      <c r="AA31" s="89"/>
+      <c r="AB31" s="89"/>
+      <c r="AC31" s="90"/>
+      <c r="AD31" s="91"/>
+      <c r="AE31" s="90"/>
       <c r="AF31" s="2"/>
       <c r="AG31" s="2"/>
       <c r="AH31" s="2"/>
     </row>
-    <row r="32" ht="43.5" customHeight="1">
-      <c r="A32" s="64">
-        <v>14.0</v>
+    <row r="32" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="40">
+        <v>14</v>
       </c>
-      <c r="B32" s="90"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="85"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="87"/>
-      <c r="M32" s="85"/>
-      <c r="N32" s="32"/>
+      <c r="B32" s="92"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="51"/>
+      <c r="M32" s="49"/>
+      <c r="N32" s="22"/>
       <c r="O32" s="88"/>
-      <c r="P32" s="51"/>
+      <c r="P32" s="90"/>
       <c r="Q32" s="88"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="51"/>
+      <c r="R32" s="89"/>
+      <c r="S32" s="89"/>
+      <c r="T32" s="89"/>
+      <c r="U32" s="89"/>
+      <c r="V32" s="89"/>
+      <c r="W32" s="89"/>
+      <c r="X32" s="90"/>
       <c r="Y32" s="88"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="29"/>
-      <c r="AC32" s="51"/>
-      <c r="AD32" s="89"/>
-      <c r="AE32" s="51"/>
+      <c r="Z32" s="89"/>
+      <c r="AA32" s="89"/>
+      <c r="AB32" s="89"/>
+      <c r="AC32" s="90"/>
+      <c r="AD32" s="91"/>
+      <c r="AE32" s="90"/>
       <c r="AF32" s="2"/>
       <c r="AG32" s="2"/>
       <c r="AH32" s="2"/>
     </row>
-    <row r="33" ht="43.5" customHeight="1">
-      <c r="A33" s="64">
-        <v>15.0</v>
+    <row r="33" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="40">
+        <v>15</v>
       </c>
-      <c r="B33" s="90"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="85"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="85"/>
-      <c r="K33" s="86"/>
-      <c r="L33" s="87"/>
-      <c r="M33" s="85"/>
-      <c r="N33" s="91"/>
+      <c r="B33" s="92"/>
+      <c r="C33" s="89"/>
+      <c r="D33" s="89"/>
+      <c r="E33" s="89"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="50"/>
+      <c r="L33" s="51"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="52"/>
       <c r="O33" s="88"/>
-      <c r="P33" s="51"/>
+      <c r="P33" s="90"/>
       <c r="Q33" s="88"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="29"/>
-      <c r="T33" s="29"/>
-      <c r="U33" s="29"/>
-      <c r="V33" s="29"/>
-      <c r="W33" s="29"/>
-      <c r="X33" s="51"/>
+      <c r="R33" s="89"/>
+      <c r="S33" s="89"/>
+      <c r="T33" s="89"/>
+      <c r="U33" s="89"/>
+      <c r="V33" s="89"/>
+      <c r="W33" s="89"/>
+      <c r="X33" s="90"/>
       <c r="Y33" s="88"/>
-      <c r="Z33" s="29"/>
-      <c r="AA33" s="29"/>
-      <c r="AB33" s="29"/>
-      <c r="AC33" s="51"/>
-      <c r="AD33" s="89"/>
-      <c r="AE33" s="51"/>
+      <c r="Z33" s="89"/>
+      <c r="AA33" s="89"/>
+      <c r="AB33" s="89"/>
+      <c r="AC33" s="90"/>
+      <c r="AD33" s="91"/>
+      <c r="AE33" s="90"/>
       <c r="AF33" s="2"/>
       <c r="AG33" s="2"/>
       <c r="AH33" s="2"/>
     </row>
-    <row r="34" ht="60.0" customHeight="1">
-      <c r="A34" s="64">
-        <v>16.0</v>
+    <row r="34" spans="1:34" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="40">
+        <v>16</v>
       </c>
-      <c r="B34" s="90"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="85"/>
-      <c r="I34" s="51"/>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="87"/>
-      <c r="M34" s="85"/>
-      <c r="N34" s="91"/>
+      <c r="B34" s="92"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="89"/>
+      <c r="G34" s="90"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="90"/>
+      <c r="J34" s="49"/>
+      <c r="K34" s="50"/>
+      <c r="L34" s="51"/>
+      <c r="M34" s="49"/>
+      <c r="N34" s="52"/>
       <c r="O34" s="88"/>
-      <c r="P34" s="51"/>
+      <c r="P34" s="90"/>
       <c r="Q34" s="88"/>
-      <c r="R34" s="29"/>
-      <c r="S34" s="29"/>
-      <c r="T34" s="29"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="29"/>
-      <c r="W34" s="29"/>
-      <c r="X34" s="51"/>
+      <c r="R34" s="89"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="89"/>
+      <c r="V34" s="89"/>
+      <c r="W34" s="89"/>
+      <c r="X34" s="90"/>
       <c r="Y34" s="88"/>
-      <c r="Z34" s="29"/>
-      <c r="AA34" s="29"/>
-      <c r="AB34" s="29"/>
-      <c r="AC34" s="51"/>
-      <c r="AD34" s="92"/>
-      <c r="AE34" s="51"/>
+      <c r="Z34" s="89"/>
+      <c r="AA34" s="89"/>
+      <c r="AB34" s="89"/>
+      <c r="AC34" s="90"/>
+      <c r="AD34" s="129"/>
+      <c r="AE34" s="90"/>
       <c r="AF34" s="2"/>
       <c r="AG34" s="2"/>
       <c r="AH34" s="2"/>
     </row>
-    <row r="35" ht="43.5" customHeight="1">
-      <c r="A35" s="64">
-        <v>17.0</v>
+    <row r="35" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="40">
+        <v>17</v>
       </c>
-      <c r="B35" s="93"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="85"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="64"/>
-      <c r="K35" s="86"/>
-      <c r="L35" s="87"/>
-      <c r="M35" s="91"/>
-      <c r="N35" s="91"/>
+      <c r="B35" s="127"/>
+      <c r="C35" s="89"/>
+      <c r="D35" s="89"/>
+      <c r="E35" s="89"/>
+      <c r="F35" s="89"/>
+      <c r="G35" s="90"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="90"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="50"/>
+      <c r="L35" s="51"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
       <c r="O35" s="88"/>
-      <c r="P35" s="51"/>
+      <c r="P35" s="90"/>
       <c r="Q35" s="88"/>
-      <c r="R35" s="29"/>
-      <c r="S35" s="29"/>
-      <c r="T35" s="29"/>
-      <c r="U35" s="29"/>
-      <c r="V35" s="29"/>
-      <c r="W35" s="29"/>
-      <c r="X35" s="51"/>
+      <c r="R35" s="89"/>
+      <c r="S35" s="89"/>
+      <c r="T35" s="89"/>
+      <c r="U35" s="89"/>
+      <c r="V35" s="89"/>
+      <c r="W35" s="89"/>
+      <c r="X35" s="90"/>
       <c r="Y35" s="88"/>
-      <c r="Z35" s="29"/>
-      <c r="AA35" s="29"/>
-      <c r="AB35" s="29"/>
-      <c r="AC35" s="51"/>
-      <c r="AD35" s="92"/>
-      <c r="AE35" s="51"/>
+      <c r="Z35" s="89"/>
+      <c r="AA35" s="89"/>
+      <c r="AB35" s="89"/>
+      <c r="AC35" s="90"/>
+      <c r="AD35" s="129"/>
+      <c r="AE35" s="90"/>
       <c r="AF35" s="2"/>
       <c r="AG35" s="2"/>
       <c r="AH35" s="2"/>
     </row>
-    <row r="36" ht="43.5" customHeight="1">
-      <c r="A36" s="64">
-        <v>18.0</v>
+    <row r="36" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="40">
+        <v>18</v>
       </c>
-      <c r="B36" s="85"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="85"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="64"/>
-      <c r="K36" s="86"/>
-      <c r="L36" s="94"/>
-      <c r="M36" s="91"/>
-      <c r="N36" s="91"/>
+      <c r="B36" s="93"/>
+      <c r="C36" s="89"/>
+      <c r="D36" s="89"/>
+      <c r="E36" s="89"/>
+      <c r="F36" s="89"/>
+      <c r="G36" s="90"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="90"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="50"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="52"/>
       <c r="O36" s="88"/>
-      <c r="P36" s="51"/>
+      <c r="P36" s="90"/>
       <c r="Q36" s="88"/>
-      <c r="R36" s="29"/>
-      <c r="S36" s="29"/>
-      <c r="T36" s="29"/>
-      <c r="U36" s="29"/>
-      <c r="V36" s="29"/>
-      <c r="W36" s="29"/>
-      <c r="X36" s="51"/>
+      <c r="R36" s="89"/>
+      <c r="S36" s="89"/>
+      <c r="T36" s="89"/>
+      <c r="U36" s="89"/>
+      <c r="V36" s="89"/>
+      <c r="W36" s="89"/>
+      <c r="X36" s="90"/>
       <c r="Y36" s="88"/>
-      <c r="Z36" s="29"/>
-      <c r="AA36" s="29"/>
-      <c r="AB36" s="29"/>
-      <c r="AC36" s="51"/>
-      <c r="AD36" s="92"/>
-      <c r="AE36" s="51"/>
+      <c r="Z36" s="89"/>
+      <c r="AA36" s="89"/>
+      <c r="AB36" s="89"/>
+      <c r="AC36" s="90"/>
+      <c r="AD36" s="129"/>
+      <c r="AE36" s="90"/>
       <c r="AF36" s="2"/>
       <c r="AG36" s="2"/>
       <c r="AH36" s="2"/>
     </row>
-    <row r="37" ht="43.5" customHeight="1">
-      <c r="A37" s="64">
-        <v>19.0</v>
+    <row r="37" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="40">
+        <v>19</v>
       </c>
-      <c r="B37" s="85"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="85"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="64"/>
-      <c r="K37" s="86"/>
-      <c r="L37" s="94"/>
-      <c r="M37" s="91"/>
-      <c r="N37" s="91"/>
+      <c r="B37" s="93"/>
+      <c r="C37" s="89"/>
+      <c r="D37" s="89"/>
+      <c r="E37" s="89"/>
+      <c r="F37" s="89"/>
+      <c r="G37" s="90"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="90"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="50"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="52"/>
+      <c r="N37" s="52"/>
       <c r="O37" s="88"/>
-      <c r="P37" s="51"/>
+      <c r="P37" s="90"/>
       <c r="Q37" s="88"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="51"/>
+      <c r="R37" s="89"/>
+      <c r="S37" s="89"/>
+      <c r="T37" s="89"/>
+      <c r="U37" s="89"/>
+      <c r="V37" s="89"/>
+      <c r="W37" s="89"/>
+      <c r="X37" s="90"/>
       <c r="Y37" s="88"/>
-      <c r="Z37" s="29"/>
-      <c r="AA37" s="29"/>
-      <c r="AB37" s="29"/>
-      <c r="AC37" s="51"/>
-      <c r="AD37" s="92"/>
-      <c r="AE37" s="51"/>
+      <c r="Z37" s="89"/>
+      <c r="AA37" s="89"/>
+      <c r="AB37" s="89"/>
+      <c r="AC37" s="90"/>
+      <c r="AD37" s="129"/>
+      <c r="AE37" s="90"/>
       <c r="AF37" s="2"/>
       <c r="AG37" s="2"/>
       <c r="AH37" s="2"/>
     </row>
-    <row r="38" ht="43.5" customHeight="1">
-      <c r="A38" s="64">
-        <v>20.0</v>
+    <row r="38" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="40">
+        <v>20</v>
       </c>
-      <c r="B38" s="60" t="s">
-        <v>42</v>
+      <c r="B38" s="112" t="s">
+        <v>40</v>
       </c>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="51"/>
-      <c r="M38" s="91"/>
-      <c r="N38" s="91"/>
-      <c r="O38" s="76"/>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="76"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="29"/>
-      <c r="T38" s="29"/>
-      <c r="U38" s="29"/>
-      <c r="V38" s="29"/>
-      <c r="W38" s="29"/>
-      <c r="X38" s="51"/>
-      <c r="Y38" s="76"/>
-      <c r="Z38" s="29"/>
-      <c r="AA38" s="29"/>
-      <c r="AB38" s="29"/>
-      <c r="AC38" s="51"/>
-      <c r="AD38" s="95"/>
-      <c r="AE38" s="51"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
+      <c r="I38" s="89"/>
+      <c r="J38" s="89"/>
+      <c r="K38" s="89"/>
+      <c r="L38" s="90"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+      <c r="O38" s="121"/>
+      <c r="P38" s="90"/>
+      <c r="Q38" s="121"/>
+      <c r="R38" s="89"/>
+      <c r="S38" s="89"/>
+      <c r="T38" s="89"/>
+      <c r="U38" s="89"/>
+      <c r="V38" s="89"/>
+      <c r="W38" s="89"/>
+      <c r="X38" s="90"/>
+      <c r="Y38" s="121"/>
+      <c r="Z38" s="89"/>
+      <c r="AA38" s="89"/>
+      <c r="AB38" s="89"/>
+      <c r="AC38" s="90"/>
+      <c r="AD38" s="139"/>
+      <c r="AE38" s="90"/>
       <c r="AF38" s="2"/>
       <c r="AG38" s="2"/>
       <c r="AH38" s="2"/>
     </row>
-    <row r="39" ht="9.0" customHeight="1">
-      <c r="A39" s="96"/>
-      <c r="B39" s="97"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="97"/>
-      <c r="J39" s="97"/>
-      <c r="K39" s="97"/>
-      <c r="L39" s="97"/>
+    <row r="39" spans="1:34" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="54"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="55"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
-      <c r="P39" s="98"/>
-      <c r="Q39" s="99"/>
+      <c r="P39" s="56"/>
+      <c r="Q39" s="57"/>
       <c r="R39" s="2"/>
-      <c r="S39" s="98"/>
-      <c r="T39" s="98"/>
-      <c r="U39" s="98"/>
-      <c r="V39" s="98"/>
-      <c r="W39" s="98"/>
-      <c r="X39" s="98"/>
-      <c r="Y39" s="98"/>
-      <c r="Z39" s="98"/>
-      <c r="AA39" s="98"/>
-      <c r="AB39" s="100"/>
-      <c r="AC39" s="100"/>
-      <c r="AD39" s="100"/>
-      <c r="AE39" s="101"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="56"/>
+      <c r="U39" s="56"/>
+      <c r="V39" s="56"/>
+      <c r="W39" s="56"/>
+      <c r="X39" s="56"/>
+      <c r="Y39" s="56"/>
+      <c r="Z39" s="56"/>
+      <c r="AA39" s="56"/>
+      <c r="AB39" s="58"/>
+      <c r="AC39" s="58"/>
+      <c r="AD39" s="58"/>
+      <c r="AE39" s="59"/>
       <c r="AF39" s="2"/>
       <c r="AG39" s="2"/>
       <c r="AH39" s="2"/>
     </row>
-    <row r="40" ht="4.5" customHeight="1">
+    <row r="40" spans="1:34" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2863,271 +3106,297 @@
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
-      <c r="P40" s="102"/>
+      <c r="P40" s="60"/>
       <c r="Q40" s="2"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="19"/>
+      <c r="R40" s="19"/>
+      <c r="S40" s="11"/>
       <c r="T40" s="2"/>
-      <c r="U40" s="102"/>
-      <c r="V40" s="102"/>
-      <c r="W40" s="102"/>
-      <c r="X40" s="102"/>
-      <c r="Y40" s="102"/>
+      <c r="U40" s="60"/>
+      <c r="V40" s="60"/>
+      <c r="W40" s="60"/>
+      <c r="X40" s="60"/>
+      <c r="Y40" s="60"/>
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
-      <c r="AB40" s="19"/>
+      <c r="AB40" s="11"/>
       <c r="AC40" s="2"/>
-      <c r="AD40" s="102"/>
-      <c r="AE40" s="103"/>
+      <c r="AD40" s="60"/>
+      <c r="AE40" s="61"/>
       <c r="AF40" s="2"/>
       <c r="AG40" s="2"/>
       <c r="AH40" s="2"/>
     </row>
-    <row r="41" ht="24.0" customHeight="1">
-      <c r="A41" s="104" t="s">
-        <v>43</v>
+    <row r="41" spans="1:34" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="62" t="s">
+        <v>41</v>
       </c>
-      <c r="B41" s="105"/>
-      <c r="C41" s="105"/>
-      <c r="D41" s="105"/>
-      <c r="E41" s="105"/>
-      <c r="F41" s="105"/>
-      <c r="G41" s="105"/>
-      <c r="H41" s="106" t="s">
-        <v>36</v>
+      <c r="B41" s="63"/>
+      <c r="C41" s="63"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="64" t="s">
+        <v>34</v>
       </c>
-      <c r="I41" s="107"/>
-      <c r="J41" s="60" t="s">
-        <v>37</v>
+      <c r="I41" s="65"/>
+      <c r="J41" s="112" t="s">
+        <v>35</v>
       </c>
-      <c r="K41" s="29"/>
-      <c r="L41" s="108"/>
-      <c r="M41" s="109"/>
-      <c r="N41" s="110" t="s">
-        <v>44</v>
+      <c r="K41" s="89"/>
+      <c r="L41" s="66"/>
+      <c r="M41" s="67"/>
+      <c r="N41" s="140" t="s">
+        <v>42</v>
       </c>
-      <c r="O41" s="111"/>
-      <c r="P41" s="111"/>
-      <c r="Q41" s="111"/>
-      <c r="R41" s="111"/>
-      <c r="S41" s="111"/>
-      <c r="T41" s="111"/>
-      <c r="U41" s="111"/>
-      <c r="V41" s="111"/>
-      <c r="W41" s="111"/>
-      <c r="X41" s="111"/>
-      <c r="Y41" s="111"/>
-      <c r="Z41" s="111"/>
-      <c r="AA41" s="111"/>
-      <c r="AB41" s="111"/>
-      <c r="AC41" s="111"/>
-      <c r="AD41" s="111"/>
-      <c r="AE41" s="112"/>
+      <c r="O41" s="141"/>
+      <c r="P41" s="141"/>
+      <c r="Q41" s="141"/>
+      <c r="R41" s="141"/>
+      <c r="S41" s="141"/>
+      <c r="T41" s="141"/>
+      <c r="U41" s="141"/>
+      <c r="V41" s="141"/>
+      <c r="W41" s="141"/>
+      <c r="X41" s="141"/>
+      <c r="Y41" s="141"/>
+      <c r="Z41" s="141"/>
+      <c r="AA41" s="141"/>
+      <c r="AB41" s="141"/>
+      <c r="AC41" s="141"/>
+      <c r="AD41" s="141"/>
+      <c r="AE41" s="142"/>
       <c r="AF41" s="2"/>
       <c r="AG41" s="2"/>
       <c r="AH41" s="2"/>
     </row>
-    <row r="42" ht="9.0" customHeight="1">
-      <c r="A42" s="113"/>
-      <c r="B42" s="114"/>
-      <c r="C42" s="114"/>
-      <c r="D42" s="114"/>
-      <c r="E42" s="114"/>
-      <c r="F42" s="114"/>
-      <c r="G42" s="114"/>
-      <c r="H42" s="114"/>
-      <c r="I42" s="114"/>
-      <c r="J42" s="115"/>
-      <c r="K42" s="115"/>
-      <c r="L42" s="115"/>
-      <c r="M42" s="115"/>
-      <c r="N42" s="116" t="s">
+    <row r="42" spans="1:34" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="68"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="69"/>
+      <c r="F42" s="69"/>
+      <c r="G42" s="69"/>
+      <c r="H42" s="69"/>
+      <c r="I42" s="69"/>
+      <c r="J42" s="70"/>
+      <c r="K42" s="70"/>
+      <c r="L42" s="70"/>
+      <c r="M42" s="70"/>
+      <c r="N42" s="131" t="s">
+        <v>43</v>
+      </c>
+      <c r="O42" s="104"/>
+      <c r="P42" s="104"/>
+      <c r="Q42" s="104"/>
+      <c r="R42" s="104"/>
+      <c r="S42" s="104"/>
+      <c r="T42" s="104"/>
+      <c r="U42" s="104"/>
+      <c r="V42" s="104"/>
+      <c r="W42" s="104"/>
+      <c r="X42" s="104"/>
+      <c r="Y42" s="104"/>
+      <c r="Z42" s="104"/>
+      <c r="AA42" s="105"/>
+      <c r="AB42" s="143" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC42" s="104"/>
+      <c r="AD42" s="105"/>
+      <c r="AE42" s="132" t="s">
         <v>45</v>
-      </c>
-      <c r="O42" s="34"/>
-      <c r="P42" s="34"/>
-      <c r="Q42" s="34"/>
-      <c r="R42" s="34"/>
-      <c r="S42" s="34"/>
-      <c r="T42" s="34"/>
-      <c r="U42" s="34"/>
-      <c r="V42" s="34"/>
-      <c r="W42" s="34"/>
-      <c r="X42" s="34"/>
-      <c r="Y42" s="34"/>
-      <c r="Z42" s="34"/>
-      <c r="AA42" s="35"/>
-      <c r="AB42" s="117" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC42" s="34"/>
-      <c r="AD42" s="35"/>
-      <c r="AE42" s="118" t="s">
-        <v>47</v>
       </c>
       <c r="AF42" s="2"/>
       <c r="AG42" s="2"/>
       <c r="AH42" s="2"/>
     </row>
-    <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="119" t="s">
-        <v>48</v>
+    <row r="43" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="71" t="s">
+        <v>46</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="120"/>
-      <c r="J43" s="120"/>
-      <c r="K43" s="120"/>
-      <c r="L43" s="121"/>
-      <c r="M43" s="122"/>
-      <c r="N43" s="44"/>
-      <c r="O43" s="45"/>
-      <c r="P43" s="45"/>
-      <c r="Q43" s="45"/>
-      <c r="R43" s="45"/>
-      <c r="S43" s="45"/>
-      <c r="T43" s="45"/>
-      <c r="U43" s="45"/>
-      <c r="V43" s="45"/>
-      <c r="W43" s="45"/>
-      <c r="X43" s="45"/>
-      <c r="Y43" s="45"/>
-      <c r="Z43" s="45"/>
-      <c r="AA43" s="46"/>
-      <c r="AB43" s="45"/>
-      <c r="AC43" s="45"/>
-      <c r="AD43" s="46"/>
-      <c r="AE43" s="123"/>
-      <c r="AF43" s="27"/>
-      <c r="AG43" s="27"/>
-      <c r="AH43" s="27"/>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="124"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
-      <c r="K44" s="27"/>
-      <c r="L44" s="125"/>
-      <c r="M44" s="115"/>
-      <c r="N44" s="126"/>
-      <c r="O44" s="34"/>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="34"/>
-      <c r="R44" s="34"/>
-      <c r="S44" s="34"/>
-      <c r="T44" s="34"/>
-      <c r="U44" s="34"/>
-      <c r="V44" s="34"/>
-      <c r="W44" s="34"/>
-      <c r="X44" s="34"/>
-      <c r="Y44" s="34"/>
-      <c r="Z44" s="34"/>
-      <c r="AA44" s="35"/>
-      <c r="AB44" s="127"/>
-      <c r="AC44" s="34"/>
-      <c r="AD44" s="35"/>
-      <c r="AE44" s="118"/>
-      <c r="AF44" s="27"/>
-      <c r="AG44" s="27"/>
-      <c r="AH44" s="27"/>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="124"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="125"/>
-      <c r="M45" s="122"/>
-      <c r="N45" s="66"/>
-      <c r="AA45" s="67"/>
-      <c r="AB45" s="66"/>
-      <c r="AD45" s="67"/>
-      <c r="AE45" s="128"/>
-      <c r="AF45" s="27"/>
-      <c r="AG45" s="27"/>
-      <c r="AH45" s="27"/>
-    </row>
-    <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="129" t="s">
-        <v>49</v>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="72"/>
+      <c r="J43" s="72"/>
+      <c r="K43" s="72"/>
+      <c r="L43" s="73"/>
+      <c r="M43" s="74"/>
+      <c r="N43" s="106"/>
+      <c r="O43" s="107"/>
+      <c r="P43" s="107"/>
+      <c r="Q43" s="107"/>
+      <c r="R43" s="107"/>
+      <c r="S43" s="107"/>
+      <c r="T43" s="107"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="107"/>
+      <c r="W43" s="107"/>
+      <c r="X43" s="107"/>
+      <c r="Y43" s="107"/>
+      <c r="Z43" s="107"/>
+      <c r="AA43" s="108"/>
+      <c r="AB43" s="107"/>
+      <c r="AC43" s="107"/>
+      <c r="AD43" s="108"/>
+      <c r="AE43" s="134"/>
+      <c r="AF43" s="19"/>
+      <c r="AG43" s="19"/>
+      <c r="AH43" s="19"/>
+    </row>
+    <row r="44" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="75"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="76"/>
+      <c r="M44" s="70"/>
+      <c r="N44" s="130"/>
+      <c r="O44" s="104"/>
+      <c r="P44" s="104"/>
+      <c r="Q44" s="104"/>
+      <c r="R44" s="104"/>
+      <c r="S44" s="104"/>
+      <c r="T44" s="104"/>
+      <c r="U44" s="104"/>
+      <c r="V44" s="104"/>
+      <c r="W44" s="104"/>
+      <c r="X44" s="104"/>
+      <c r="Y44" s="104"/>
+      <c r="Z44" s="104"/>
+      <c r="AA44" s="105"/>
+      <c r="AB44" s="144"/>
+      <c r="AC44" s="104"/>
+      <c r="AD44" s="105"/>
+      <c r="AE44" s="132"/>
+      <c r="AF44" s="19"/>
+      <c r="AG44" s="19"/>
+      <c r="AH44" s="19"/>
+    </row>
+    <row r="45" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="75"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="76"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="114"/>
+      <c r="O45" s="99"/>
+      <c r="P45" s="99"/>
+      <c r="Q45" s="99"/>
+      <c r="R45" s="99"/>
+      <c r="S45" s="99"/>
+      <c r="T45" s="99"/>
+      <c r="U45" s="99"/>
+      <c r="V45" s="99"/>
+      <c r="W45" s="99"/>
+      <c r="X45" s="99"/>
+      <c r="Y45" s="99"/>
+      <c r="Z45" s="99"/>
+      <c r="AA45" s="115"/>
+      <c r="AB45" s="114"/>
+      <c r="AC45" s="99"/>
+      <c r="AD45" s="115"/>
+      <c r="AE45" s="133"/>
+      <c r="AF45" s="19"/>
+      <c r="AG45" s="19"/>
+      <c r="AH45" s="19"/>
+    </row>
+    <row r="46" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="102"/>
-      <c r="G46" s="102"/>
-      <c r="H46" s="130"/>
-      <c r="I46" s="130"/>
-      <c r="J46" s="130"/>
-      <c r="K46" s="130"/>
-      <c r="L46" s="131"/>
-      <c r="M46" s="115"/>
-      <c r="N46" s="66"/>
-      <c r="AA46" s="67"/>
-      <c r="AB46" s="66"/>
-      <c r="AD46" s="67"/>
-      <c r="AE46" s="128"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="60"/>
+      <c r="H46" s="77"/>
+      <c r="I46" s="77"/>
+      <c r="J46" s="77"/>
+      <c r="K46" s="77"/>
+      <c r="L46" s="78"/>
+      <c r="M46" s="70"/>
+      <c r="N46" s="114"/>
+      <c r="O46" s="99"/>
+      <c r="P46" s="99"/>
+      <c r="Q46" s="99"/>
+      <c r="R46" s="99"/>
+      <c r="S46" s="99"/>
+      <c r="T46" s="99"/>
+      <c r="U46" s="99"/>
+      <c r="V46" s="99"/>
+      <c r="W46" s="99"/>
+      <c r="X46" s="99"/>
+      <c r="Y46" s="99"/>
+      <c r="Z46" s="99"/>
+      <c r="AA46" s="115"/>
+      <c r="AB46" s="114"/>
+      <c r="AC46" s="99"/>
+      <c r="AD46" s="115"/>
+      <c r="AE46" s="133"/>
       <c r="AF46" s="2"/>
       <c r="AG46" s="2"/>
       <c r="AH46" s="2"/>
     </row>
-    <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="132"/>
-      <c r="B47" s="133"/>
-      <c r="C47" s="133"/>
-      <c r="D47" s="133"/>
-      <c r="E47" s="133"/>
-      <c r="F47" s="134"/>
-      <c r="G47" s="134"/>
-      <c r="H47" s="134"/>
-      <c r="I47" s="134"/>
-      <c r="J47" s="134"/>
-      <c r="K47" s="135"/>
-      <c r="L47" s="136"/>
-      <c r="M47" s="122"/>
-      <c r="N47" s="44"/>
-      <c r="O47" s="45"/>
-      <c r="P47" s="45"/>
-      <c r="Q47" s="45"/>
-      <c r="R47" s="45"/>
-      <c r="S47" s="45"/>
-      <c r="T47" s="45"/>
-      <c r="U47" s="45"/>
-      <c r="V47" s="45"/>
-      <c r="W47" s="45"/>
-      <c r="X47" s="45"/>
-      <c r="Y47" s="45"/>
-      <c r="Z47" s="45"/>
-      <c r="AA47" s="46"/>
-      <c r="AB47" s="44"/>
-      <c r="AC47" s="45"/>
-      <c r="AD47" s="46"/>
-      <c r="AE47" s="123"/>
+    <row r="47" spans="1:34" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="79"/>
+      <c r="B47" s="80"/>
+      <c r="C47" s="80"/>
+      <c r="D47" s="80"/>
+      <c r="E47" s="80"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="81"/>
+      <c r="H47" s="81"/>
+      <c r="I47" s="81"/>
+      <c r="J47" s="81"/>
+      <c r="K47" s="82"/>
+      <c r="L47" s="83"/>
+      <c r="M47" s="74"/>
+      <c r="N47" s="106"/>
+      <c r="O47" s="107"/>
+      <c r="P47" s="107"/>
+      <c r="Q47" s="107"/>
+      <c r="R47" s="107"/>
+      <c r="S47" s="107"/>
+      <c r="T47" s="107"/>
+      <c r="U47" s="107"/>
+      <c r="V47" s="107"/>
+      <c r="W47" s="107"/>
+      <c r="X47" s="107"/>
+      <c r="Y47" s="107"/>
+      <c r="Z47" s="107"/>
+      <c r="AA47" s="108"/>
+      <c r="AB47" s="106"/>
+      <c r="AC47" s="107"/>
+      <c r="AD47" s="108"/>
+      <c r="AE47" s="134"/>
       <c r="AF47" s="2"/>
       <c r="AG47" s="2"/>
       <c r="AH47" s="2"/>
     </row>
-    <row r="48" ht="6.75" customHeight="1">
+    <row r="48" spans="1:34" ht="6.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3138,59 +3407,72 @@
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-      <c r="K48" s="27"/>
-      <c r="L48" s="27"/>
-      <c r="M48" s="115"/>
-      <c r="N48" s="126"/>
-      <c r="O48" s="34"/>
-      <c r="P48" s="34"/>
-      <c r="Q48" s="34"/>
-      <c r="R48" s="34"/>
-      <c r="S48" s="34"/>
-      <c r="T48" s="34"/>
-      <c r="U48" s="34"/>
-      <c r="V48" s="34"/>
-      <c r="W48" s="34"/>
-      <c r="X48" s="34"/>
-      <c r="Y48" s="34"/>
-      <c r="Z48" s="34"/>
-      <c r="AA48" s="35"/>
-      <c r="AB48" s="116"/>
-      <c r="AC48" s="34"/>
-      <c r="AD48" s="35"/>
-      <c r="AE48" s="118"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="70"/>
+      <c r="N48" s="130"/>
+      <c r="O48" s="104"/>
+      <c r="P48" s="104"/>
+      <c r="Q48" s="104"/>
+      <c r="R48" s="104"/>
+      <c r="S48" s="104"/>
+      <c r="T48" s="104"/>
+      <c r="U48" s="104"/>
+      <c r="V48" s="104"/>
+      <c r="W48" s="104"/>
+      <c r="X48" s="104"/>
+      <c r="Y48" s="104"/>
+      <c r="Z48" s="104"/>
+      <c r="AA48" s="105"/>
+      <c r="AB48" s="131"/>
+      <c r="AC48" s="104"/>
+      <c r="AD48" s="105"/>
+      <c r="AE48" s="132"/>
       <c r="AF48" s="2"/>
       <c r="AG48" s="2"/>
       <c r="AH48" s="2"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B49" s="2"/>
-      <c r="C49" s="137"/>
-      <c r="D49" s="137"/>
+      <c r="C49" s="84"/>
+      <c r="D49" s="84"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="66"/>
-      <c r="AA49" s="67"/>
-      <c r="AB49" s="66"/>
-      <c r="AD49" s="67"/>
-      <c r="AE49" s="128"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="114"/>
+      <c r="O49" s="99"/>
+      <c r="P49" s="99"/>
+      <c r="Q49" s="99"/>
+      <c r="R49" s="99"/>
+      <c r="S49" s="99"/>
+      <c r="T49" s="99"/>
+      <c r="U49" s="99"/>
+      <c r="V49" s="99"/>
+      <c r="W49" s="99"/>
+      <c r="X49" s="99"/>
+      <c r="Y49" s="99"/>
+      <c r="Z49" s="99"/>
+      <c r="AA49" s="115"/>
+      <c r="AB49" s="114"/>
+      <c r="AC49" s="99"/>
+      <c r="AD49" s="115"/>
+      <c r="AE49" s="133"/>
       <c r="AF49" s="2"/>
       <c r="AG49" s="2"/>
       <c r="AH49" s="2"/>
     </row>
-    <row r="50" ht="21.0" customHeight="1">
+    <row r="50" spans="1:34" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3204,22 +3486,35 @@
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
-      <c r="N50" s="66"/>
-      <c r="AA50" s="67"/>
-      <c r="AB50" s="66"/>
-      <c r="AD50" s="67"/>
-      <c r="AE50" s="128"/>
+      <c r="N50" s="114"/>
+      <c r="O50" s="99"/>
+      <c r="P50" s="99"/>
+      <c r="Q50" s="99"/>
+      <c r="R50" s="99"/>
+      <c r="S50" s="99"/>
+      <c r="T50" s="99"/>
+      <c r="U50" s="99"/>
+      <c r="V50" s="99"/>
+      <c r="W50" s="99"/>
+      <c r="X50" s="99"/>
+      <c r="Y50" s="99"/>
+      <c r="Z50" s="99"/>
+      <c r="AA50" s="115"/>
+      <c r="AB50" s="114"/>
+      <c r="AC50" s="99"/>
+      <c r="AD50" s="115"/>
+      <c r="AE50" s="133"/>
       <c r="AF50" s="2"/>
       <c r="AG50" s="2"/>
       <c r="AH50" s="2"/>
     </row>
-    <row r="51" ht="18.75" customHeight="1">
+    <row r="51" spans="1:34" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="138"/>
-      <c r="F51" s="138"/>
+      <c r="E51" s="85"/>
+      <c r="F51" s="85"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
@@ -3227,29 +3522,29 @@
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
-      <c r="N51" s="44"/>
-      <c r="O51" s="45"/>
-      <c r="P51" s="45"/>
-      <c r="Q51" s="45"/>
-      <c r="R51" s="45"/>
-      <c r="S51" s="45"/>
-      <c r="T51" s="45"/>
-      <c r="U51" s="45"/>
-      <c r="V51" s="45"/>
-      <c r="W51" s="45"/>
-      <c r="X51" s="45"/>
-      <c r="Y51" s="45"/>
-      <c r="Z51" s="45"/>
-      <c r="AA51" s="46"/>
-      <c r="AB51" s="44"/>
-      <c r="AC51" s="45"/>
-      <c r="AD51" s="46"/>
-      <c r="AE51" s="123"/>
+      <c r="N51" s="106"/>
+      <c r="O51" s="107"/>
+      <c r="P51" s="107"/>
+      <c r="Q51" s="107"/>
+      <c r="R51" s="107"/>
+      <c r="S51" s="107"/>
+      <c r="T51" s="107"/>
+      <c r="U51" s="107"/>
+      <c r="V51" s="107"/>
+      <c r="W51" s="107"/>
+      <c r="X51" s="107"/>
+      <c r="Y51" s="107"/>
+      <c r="Z51" s="107"/>
+      <c r="AA51" s="108"/>
+      <c r="AB51" s="106"/>
+      <c r="AC51" s="107"/>
+      <c r="AD51" s="108"/>
+      <c r="AE51" s="134"/>
       <c r="AF51" s="2"/>
       <c r="AG51" s="2"/>
       <c r="AH51" s="2"/>
     </row>
-    <row r="52" ht="16.5" customHeight="1">
+    <row r="52" spans="1:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -3263,17 +3558,29 @@
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
-      <c r="N52" s="139"/>
-      <c r="AA52" s="67"/>
-      <c r="AB52" s="140"/>
-      <c r="AC52" s="34"/>
-      <c r="AD52" s="35"/>
-      <c r="AE52" s="141"/>
+      <c r="N52" s="135"/>
+      <c r="O52" s="99"/>
+      <c r="P52" s="99"/>
+      <c r="Q52" s="99"/>
+      <c r="R52" s="99"/>
+      <c r="S52" s="99"/>
+      <c r="T52" s="99"/>
+      <c r="U52" s="99"/>
+      <c r="V52" s="99"/>
+      <c r="W52" s="99"/>
+      <c r="X52" s="99"/>
+      <c r="Y52" s="99"/>
+      <c r="Z52" s="99"/>
+      <c r="AA52" s="115"/>
+      <c r="AB52" s="128"/>
+      <c r="AC52" s="104"/>
+      <c r="AD52" s="105"/>
+      <c r="AE52" s="136"/>
       <c r="AF52" s="2"/>
       <c r="AG52" s="2"/>
       <c r="AH52" s="2"/>
     </row>
-    <row r="53" ht="22.5" customHeight="1">
+    <row r="53" spans="1:34" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -3287,16 +3594,29 @@
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
-      <c r="N53" s="66"/>
-      <c r="AA53" s="67"/>
-      <c r="AB53" s="66"/>
-      <c r="AD53" s="67"/>
-      <c r="AE53" s="128"/>
+      <c r="N53" s="114"/>
+      <c r="O53" s="99"/>
+      <c r="P53" s="99"/>
+      <c r="Q53" s="99"/>
+      <c r="R53" s="99"/>
+      <c r="S53" s="99"/>
+      <c r="T53" s="99"/>
+      <c r="U53" s="99"/>
+      <c r="V53" s="99"/>
+      <c r="W53" s="99"/>
+      <c r="X53" s="99"/>
+      <c r="Y53" s="99"/>
+      <c r="Z53" s="99"/>
+      <c r="AA53" s="115"/>
+      <c r="AB53" s="114"/>
+      <c r="AC53" s="99"/>
+      <c r="AD53" s="115"/>
+      <c r="AE53" s="133"/>
       <c r="AF53" s="2"/>
       <c r="AG53" s="2"/>
       <c r="AH53" s="2"/>
     </row>
-    <row r="54" ht="15.0" customHeight="1">
+    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -3310,16 +3630,29 @@
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
-      <c r="N54" s="66"/>
-      <c r="AA54" s="67"/>
-      <c r="AB54" s="66"/>
-      <c r="AD54" s="67"/>
-      <c r="AE54" s="128"/>
+      <c r="N54" s="114"/>
+      <c r="O54" s="99"/>
+      <c r="P54" s="99"/>
+      <c r="Q54" s="99"/>
+      <c r="R54" s="99"/>
+      <c r="S54" s="99"/>
+      <c r="T54" s="99"/>
+      <c r="U54" s="99"/>
+      <c r="V54" s="99"/>
+      <c r="W54" s="99"/>
+      <c r="X54" s="99"/>
+      <c r="Y54" s="99"/>
+      <c r="Z54" s="99"/>
+      <c r="AA54" s="115"/>
+      <c r="AB54" s="114"/>
+      <c r="AC54" s="99"/>
+      <c r="AD54" s="115"/>
+      <c r="AE54" s="133"/>
       <c r="AF54" s="2"/>
       <c r="AG54" s="2"/>
       <c r="AH54" s="2"/>
     </row>
-    <row r="55" ht="18.0" customHeight="1">
+    <row r="55" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -3333,37 +3666,37 @@
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
-      <c r="N55" s="60" t="s">
+      <c r="N55" s="112" t="s">
+        <v>50</v>
+      </c>
+      <c r="O55" s="89"/>
+      <c r="P55" s="89"/>
+      <c r="Q55" s="89"/>
+      <c r="R55" s="89"/>
+      <c r="S55" s="90"/>
+      <c r="T55" s="131" t="s">
+        <v>51</v>
+      </c>
+      <c r="U55" s="104"/>
+      <c r="V55" s="104"/>
+      <c r="W55" s="104"/>
+      <c r="X55" s="104"/>
+      <c r="Y55" s="104"/>
+      <c r="Z55" s="105"/>
+      <c r="AA55" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
-      <c r="Q55" s="29"/>
-      <c r="R55" s="29"/>
-      <c r="S55" s="51"/>
-      <c r="T55" s="116" t="s">
+      <c r="AB55" s="104"/>
+      <c r="AC55" s="104"/>
+      <c r="AD55" s="105"/>
+      <c r="AE55" s="132" t="s">
         <v>53</v>
-      </c>
-      <c r="U55" s="34"/>
-      <c r="V55" s="34"/>
-      <c r="W55" s="34"/>
-      <c r="X55" s="34"/>
-      <c r="Y55" s="34"/>
-      <c r="Z55" s="35"/>
-      <c r="AA55" s="116" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB55" s="34"/>
-      <c r="AC55" s="34"/>
-      <c r="AD55" s="35"/>
-      <c r="AE55" s="118" t="s">
-        <v>55</v>
       </c>
       <c r="AF55" s="2"/>
       <c r="AG55" s="2"/>
       <c r="AH55" s="2"/>
     </row>
-    <row r="56" ht="18.0" customHeight="1">
+    <row r="56" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -3377,33 +3710,33 @@
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
-      <c r="N56" s="60" t="s">
-        <v>24</v>
+      <c r="N56" s="112" t="s">
+        <v>22</v>
       </c>
-      <c r="O56" s="29"/>
-      <c r="P56" s="51"/>
-      <c r="Q56" s="60" t="s">
-        <v>25</v>
+      <c r="O56" s="89"/>
+      <c r="P56" s="90"/>
+      <c r="Q56" s="112" t="s">
+        <v>23</v>
       </c>
-      <c r="R56" s="29"/>
-      <c r="S56" s="51"/>
-      <c r="T56" s="44"/>
-      <c r="U56" s="45"/>
-      <c r="V56" s="45"/>
-      <c r="W56" s="45"/>
-      <c r="X56" s="45"/>
-      <c r="Y56" s="45"/>
-      <c r="Z56" s="46"/>
-      <c r="AA56" s="44"/>
-      <c r="AB56" s="45"/>
-      <c r="AC56" s="45"/>
-      <c r="AD56" s="46"/>
-      <c r="AE56" s="123"/>
+      <c r="R56" s="89"/>
+      <c r="S56" s="90"/>
+      <c r="T56" s="106"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="107"/>
+      <c r="W56" s="107"/>
+      <c r="X56" s="107"/>
+      <c r="Y56" s="107"/>
+      <c r="Z56" s="108"/>
+      <c r="AA56" s="106"/>
+      <c r="AB56" s="107"/>
+      <c r="AC56" s="107"/>
+      <c r="AD56" s="108"/>
+      <c r="AE56" s="134"/>
       <c r="AF56" s="2"/>
       <c r="AG56" s="2"/>
       <c r="AH56" s="2"/>
     </row>
-    <row r="57" ht="18.0" customHeight="1">
+    <row r="57" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -3417,29 +3750,29 @@
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
-      <c r="N57" s="140"/>
-      <c r="O57" s="34"/>
-      <c r="P57" s="35"/>
-      <c r="Q57" s="140"/>
-      <c r="R57" s="34"/>
-      <c r="S57" s="35"/>
-      <c r="T57" s="140"/>
-      <c r="U57" s="34"/>
-      <c r="V57" s="34"/>
-      <c r="W57" s="34"/>
-      <c r="X57" s="34"/>
-      <c r="Y57" s="34"/>
-      <c r="Z57" s="35"/>
-      <c r="AA57" s="62"/>
-      <c r="AB57" s="34"/>
-      <c r="AC57" s="34"/>
-      <c r="AD57" s="35"/>
-      <c r="AE57" s="142"/>
+      <c r="N57" s="128"/>
+      <c r="O57" s="104"/>
+      <c r="P57" s="105"/>
+      <c r="Q57" s="128"/>
+      <c r="R57" s="104"/>
+      <c r="S57" s="105"/>
+      <c r="T57" s="128"/>
+      <c r="U57" s="104"/>
+      <c r="V57" s="104"/>
+      <c r="W57" s="104"/>
+      <c r="X57" s="104"/>
+      <c r="Y57" s="104"/>
+      <c r="Z57" s="105"/>
+      <c r="AA57" s="123"/>
+      <c r="AB57" s="104"/>
+      <c r="AC57" s="104"/>
+      <c r="AD57" s="105"/>
+      <c r="AE57" s="138"/>
       <c r="AF57" s="2"/>
       <c r="AG57" s="2"/>
       <c r="AH57" s="2"/>
     </row>
-    <row r="58" ht="18.0" customHeight="1">
+    <row r="58" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -3453,20 +3786,29 @@
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
-      <c r="N58" s="66"/>
-      <c r="P58" s="67"/>
-      <c r="Q58" s="66"/>
-      <c r="S58" s="67"/>
-      <c r="T58" s="66"/>
-      <c r="Z58" s="67"/>
-      <c r="AA58" s="66"/>
-      <c r="AD58" s="67"/>
-      <c r="AE58" s="128"/>
+      <c r="N58" s="114"/>
+      <c r="O58" s="99"/>
+      <c r="P58" s="115"/>
+      <c r="Q58" s="114"/>
+      <c r="R58" s="99"/>
+      <c r="S58" s="115"/>
+      <c r="T58" s="114"/>
+      <c r="U58" s="99"/>
+      <c r="V58" s="99"/>
+      <c r="W58" s="99"/>
+      <c r="X58" s="99"/>
+      <c r="Y58" s="99"/>
+      <c r="Z58" s="115"/>
+      <c r="AA58" s="114"/>
+      <c r="AB58" s="99"/>
+      <c r="AC58" s="99"/>
+      <c r="AD58" s="115"/>
+      <c r="AE58" s="133"/>
       <c r="AF58" s="2"/>
       <c r="AG58" s="2"/>
       <c r="AH58" s="2"/>
     </row>
-    <row r="59" ht="18.0" customHeight="1">
+    <row r="59" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -3480,20 +3822,29 @@
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
-      <c r="N59" s="66"/>
-      <c r="P59" s="67"/>
-      <c r="Q59" s="66"/>
-      <c r="S59" s="67"/>
-      <c r="T59" s="66"/>
-      <c r="Z59" s="67"/>
-      <c r="AA59" s="66"/>
-      <c r="AD59" s="67"/>
-      <c r="AE59" s="128"/>
+      <c r="N59" s="114"/>
+      <c r="O59" s="99"/>
+      <c r="P59" s="115"/>
+      <c r="Q59" s="114"/>
+      <c r="R59" s="99"/>
+      <c r="S59" s="115"/>
+      <c r="T59" s="114"/>
+      <c r="U59" s="99"/>
+      <c r="V59" s="99"/>
+      <c r="W59" s="99"/>
+      <c r="X59" s="99"/>
+      <c r="Y59" s="99"/>
+      <c r="Z59" s="115"/>
+      <c r="AA59" s="114"/>
+      <c r="AB59" s="99"/>
+      <c r="AC59" s="99"/>
+      <c r="AD59" s="115"/>
+      <c r="AE59" s="133"/>
       <c r="AF59" s="2"/>
       <c r="AG59" s="2"/>
       <c r="AH59" s="2"/>
     </row>
-    <row r="60" ht="18.0" customHeight="1">
+    <row r="60" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -3507,20 +3858,29 @@
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
-      <c r="N60" s="66"/>
-      <c r="P60" s="67"/>
-      <c r="Q60" s="66"/>
-      <c r="S60" s="67"/>
-      <c r="T60" s="66"/>
-      <c r="Z60" s="67"/>
-      <c r="AA60" s="66"/>
-      <c r="AD60" s="67"/>
-      <c r="AE60" s="128"/>
+      <c r="N60" s="114"/>
+      <c r="O60" s="99"/>
+      <c r="P60" s="115"/>
+      <c r="Q60" s="114"/>
+      <c r="R60" s="99"/>
+      <c r="S60" s="115"/>
+      <c r="T60" s="114"/>
+      <c r="U60" s="99"/>
+      <c r="V60" s="99"/>
+      <c r="W60" s="99"/>
+      <c r="X60" s="99"/>
+      <c r="Y60" s="99"/>
+      <c r="Z60" s="115"/>
+      <c r="AA60" s="114"/>
+      <c r="AB60" s="99"/>
+      <c r="AC60" s="99"/>
+      <c r="AD60" s="115"/>
+      <c r="AE60" s="133"/>
       <c r="AF60" s="2"/>
       <c r="AG60" s="2"/>
       <c r="AH60" s="2"/>
     </row>
-    <row r="61" ht="18.0" customHeight="1">
+    <row r="61" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3534,20 +3894,29 @@
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
-      <c r="N61" s="66"/>
-      <c r="P61" s="67"/>
-      <c r="Q61" s="66"/>
-      <c r="S61" s="67"/>
-      <c r="T61" s="66"/>
-      <c r="Z61" s="67"/>
-      <c r="AA61" s="66"/>
-      <c r="AD61" s="67"/>
-      <c r="AE61" s="128"/>
+      <c r="N61" s="114"/>
+      <c r="O61" s="99"/>
+      <c r="P61" s="115"/>
+      <c r="Q61" s="114"/>
+      <c r="R61" s="99"/>
+      <c r="S61" s="115"/>
+      <c r="T61" s="114"/>
+      <c r="U61" s="99"/>
+      <c r="V61" s="99"/>
+      <c r="W61" s="99"/>
+      <c r="X61" s="99"/>
+      <c r="Y61" s="99"/>
+      <c r="Z61" s="115"/>
+      <c r="AA61" s="114"/>
+      <c r="AB61" s="99"/>
+      <c r="AC61" s="99"/>
+      <c r="AD61" s="115"/>
+      <c r="AE61" s="133"/>
       <c r="AF61" s="2"/>
       <c r="AG61" s="2"/>
       <c r="AH61" s="2"/>
     </row>
-    <row r="62" ht="18.0" customHeight="1">
+    <row r="62" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3561,20 +3930,29 @@
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
-      <c r="N62" s="66"/>
-      <c r="P62" s="67"/>
-      <c r="Q62" s="66"/>
-      <c r="S62" s="67"/>
-      <c r="T62" s="66"/>
-      <c r="Z62" s="67"/>
-      <c r="AA62" s="66"/>
-      <c r="AD62" s="67"/>
-      <c r="AE62" s="128"/>
+      <c r="N62" s="114"/>
+      <c r="O62" s="99"/>
+      <c r="P62" s="115"/>
+      <c r="Q62" s="114"/>
+      <c r="R62" s="99"/>
+      <c r="S62" s="115"/>
+      <c r="T62" s="114"/>
+      <c r="U62" s="99"/>
+      <c r="V62" s="99"/>
+      <c r="W62" s="99"/>
+      <c r="X62" s="99"/>
+      <c r="Y62" s="99"/>
+      <c r="Z62" s="115"/>
+      <c r="AA62" s="114"/>
+      <c r="AB62" s="99"/>
+      <c r="AC62" s="99"/>
+      <c r="AD62" s="115"/>
+      <c r="AE62" s="133"/>
       <c r="AF62" s="2"/>
       <c r="AG62" s="2"/>
       <c r="AH62" s="2"/>
     </row>
-    <row r="63" ht="18.0" customHeight="1">
+    <row r="63" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3588,136 +3966,175 @@
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
-      <c r="N63" s="66"/>
-      <c r="P63" s="67"/>
-      <c r="Q63" s="66"/>
-      <c r="S63" s="67"/>
-      <c r="T63" s="66"/>
-      <c r="Z63" s="67"/>
-      <c r="AA63" s="66"/>
-      <c r="AD63" s="67"/>
-      <c r="AE63" s="128"/>
+      <c r="N63" s="114"/>
+      <c r="O63" s="99"/>
+      <c r="P63" s="115"/>
+      <c r="Q63" s="114"/>
+      <c r="R63" s="99"/>
+      <c r="S63" s="115"/>
+      <c r="T63" s="114"/>
+      <c r="U63" s="99"/>
+      <c r="V63" s="99"/>
+      <c r="W63" s="99"/>
+      <c r="X63" s="99"/>
+      <c r="Y63" s="99"/>
+      <c r="Z63" s="115"/>
+      <c r="AA63" s="114"/>
+      <c r="AB63" s="99"/>
+      <c r="AC63" s="99"/>
+      <c r="AD63" s="115"/>
+      <c r="AE63" s="133"/>
       <c r="AF63" s="2"/>
       <c r="AG63" s="2"/>
       <c r="AH63" s="2"/>
     </row>
-    <row r="64" ht="19.5" customHeight="1">
-      <c r="A64" s="143"/>
-      <c r="B64" s="144"/>
-      <c r="C64" s="144"/>
-      <c r="D64" s="144"/>
-      <c r="E64" s="144"/>
-      <c r="F64" s="144"/>
-      <c r="G64" s="144"/>
-      <c r="H64" s="144"/>
-      <c r="I64" s="144"/>
-      <c r="J64" s="144"/>
-      <c r="K64" s="144"/>
-      <c r="L64" s="144"/>
-      <c r="M64" s="144"/>
-      <c r="N64" s="44"/>
-      <c r="O64" s="45"/>
-      <c r="P64" s="46"/>
-      <c r="Q64" s="44"/>
-      <c r="R64" s="45"/>
-      <c r="S64" s="46"/>
-      <c r="T64" s="44"/>
-      <c r="U64" s="45"/>
-      <c r="V64" s="45"/>
-      <c r="W64" s="45"/>
-      <c r="X64" s="45"/>
-      <c r="Y64" s="45"/>
-      <c r="Z64" s="46"/>
-      <c r="AA64" s="44"/>
-      <c r="AB64" s="45"/>
-      <c r="AC64" s="45"/>
-      <c r="AD64" s="46"/>
-      <c r="AE64" s="123"/>
+    <row r="64" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="86"/>
+      <c r="B64" s="87"/>
+      <c r="C64" s="87"/>
+      <c r="D64" s="87"/>
+      <c r="E64" s="87"/>
+      <c r="F64" s="87"/>
+      <c r="G64" s="87"/>
+      <c r="H64" s="87"/>
+      <c r="I64" s="87"/>
+      <c r="J64" s="87"/>
+      <c r="K64" s="87"/>
+      <c r="L64" s="87"/>
+      <c r="M64" s="87"/>
+      <c r="N64" s="106"/>
+      <c r="O64" s="107"/>
+      <c r="P64" s="108"/>
+      <c r="Q64" s="106"/>
+      <c r="R64" s="107"/>
+      <c r="S64" s="108"/>
+      <c r="T64" s="106"/>
+      <c r="U64" s="107"/>
+      <c r="V64" s="107"/>
+      <c r="W64" s="107"/>
+      <c r="X64" s="107"/>
+      <c r="Y64" s="107"/>
+      <c r="Z64" s="108"/>
+      <c r="AA64" s="106"/>
+      <c r="AB64" s="107"/>
+      <c r="AC64" s="107"/>
+      <c r="AD64" s="108"/>
+      <c r="AE64" s="134"/>
       <c r="AF64" s="2"/>
       <c r="AG64" s="2"/>
       <c r="AH64" s="2"/>
     </row>
-    <row r="65" ht="43.5" customHeight="1">
-      <c r="A65" s="145" t="s">
-        <v>56</v>
+    <row r="65" spans="1:34" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="137" t="s">
+        <v>54</v>
       </c>
+      <c r="B65" s="99"/>
+      <c r="C65" s="99"/>
+      <c r="D65" s="99"/>
+      <c r="E65" s="99"/>
+      <c r="F65" s="99"/>
+      <c r="G65" s="99"/>
+      <c r="H65" s="99"/>
+      <c r="I65" s="99"/>
+      <c r="J65" s="99"/>
+      <c r="K65" s="99"/>
+      <c r="L65" s="99"/>
+      <c r="M65" s="99"/>
+      <c r="N65" s="99"/>
+      <c r="O65" s="99"/>
+      <c r="P65" s="99"/>
+      <c r="Q65" s="99"/>
+      <c r="R65" s="99"/>
+      <c r="S65" s="99"/>
+      <c r="T65" s="99"/>
+      <c r="U65" s="99"/>
+      <c r="V65" s="99"/>
+      <c r="W65" s="99"/>
+      <c r="X65" s="99"/>
+      <c r="Y65" s="99"/>
+      <c r="Z65" s="99"/>
+      <c r="AA65" s="99"/>
+      <c r="AB65" s="99"/>
+      <c r="AC65" s="99"/>
+      <c r="AD65" s="99"/>
+      <c r="AE65" s="99"/>
       <c r="AF65" s="2"/>
       <c r="AG65" s="2"/>
       <c r="AH65" s="2"/>
     </row>
-    <row r="66" ht="13.5" customHeight="1">
-      <c r="A66" s="138"/>
-      <c r="B66" s="138"/>
-      <c r="C66" s="138"/>
-      <c r="D66" s="138"/>
-      <c r="E66" s="138"/>
-      <c r="F66" s="138"/>
-      <c r="G66" s="138"/>
-      <c r="H66" s="138"/>
-      <c r="I66" s="138"/>
-      <c r="J66" s="138"/>
-      <c r="K66" s="138"/>
-      <c r="L66" s="138"/>
-      <c r="M66" s="138"/>
-      <c r="N66" s="138"/>
-      <c r="O66" s="138"/>
-      <c r="P66" s="138"/>
-      <c r="Q66" s="138"/>
-      <c r="R66" s="138"/>
-      <c r="S66" s="138"/>
-      <c r="T66" s="138"/>
-      <c r="U66" s="138"/>
-      <c r="V66" s="138"/>
-      <c r="W66" s="138"/>
-      <c r="X66" s="138"/>
-      <c r="Y66" s="138"/>
-      <c r="Z66" s="138"/>
-      <c r="AA66" s="138"/>
-      <c r="AB66" s="138"/>
-      <c r="AC66" s="138"/>
-      <c r="AD66" s="138"/>
-      <c r="AE66" s="138"/>
+    <row r="66" spans="1:34" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="85"/>
+      <c r="B66" s="85"/>
+      <c r="C66" s="85"/>
+      <c r="D66" s="85"/>
+      <c r="E66" s="85"/>
+      <c r="F66" s="85"/>
+      <c r="G66" s="85"/>
+      <c r="H66" s="85"/>
+      <c r="I66" s="85"/>
+      <c r="J66" s="85"/>
+      <c r="K66" s="85"/>
+      <c r="L66" s="85"/>
+      <c r="M66" s="85"/>
+      <c r="N66" s="85"/>
+      <c r="O66" s="85"/>
+      <c r="P66" s="85"/>
+      <c r="Q66" s="85"/>
+      <c r="R66" s="85"/>
+      <c r="S66" s="85"/>
+      <c r="T66" s="85"/>
+      <c r="U66" s="85"/>
+      <c r="V66" s="85"/>
+      <c r="W66" s="85"/>
+      <c r="X66" s="85"/>
+      <c r="Y66" s="85"/>
+      <c r="Z66" s="85"/>
+      <c r="AA66" s="85"/>
+      <c r="AB66" s="85"/>
+      <c r="AC66" s="85"/>
+      <c r="AD66" s="85"/>
+      <c r="AE66" s="85"/>
       <c r="AF66" s="2"/>
       <c r="AG66" s="2"/>
       <c r="AH66" s="2"/>
     </row>
-    <row r="67" ht="13.5" customHeight="1">
-      <c r="A67" s="138"/>
-      <c r="B67" s="138"/>
-      <c r="C67" s="138"/>
-      <c r="D67" s="138"/>
-      <c r="E67" s="138"/>
-      <c r="F67" s="138"/>
-      <c r="G67" s="138"/>
-      <c r="H67" s="138"/>
-      <c r="I67" s="138"/>
-      <c r="J67" s="138"/>
-      <c r="K67" s="138"/>
-      <c r="L67" s="138"/>
-      <c r="M67" s="138"/>
-      <c r="N67" s="138"/>
-      <c r="O67" s="138"/>
-      <c r="P67" s="138"/>
-      <c r="Q67" s="138"/>
-      <c r="R67" s="138"/>
-      <c r="S67" s="138"/>
-      <c r="T67" s="138"/>
-      <c r="U67" s="138"/>
-      <c r="V67" s="138"/>
-      <c r="W67" s="138"/>
-      <c r="X67" s="138"/>
-      <c r="Y67" s="138"/>
-      <c r="Z67" s="138"/>
-      <c r="AA67" s="138"/>
-      <c r="AB67" s="138"/>
-      <c r="AC67" s="138"/>
-      <c r="AD67" s="138"/>
-      <c r="AE67" s="138"/>
+    <row r="67" spans="1:34" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="85"/>
+      <c r="B67" s="85"/>
+      <c r="C67" s="85"/>
+      <c r="D67" s="85"/>
+      <c r="E67" s="85"/>
+      <c r="F67" s="85"/>
+      <c r="G67" s="85"/>
+      <c r="H67" s="85"/>
+      <c r="I67" s="85"/>
+      <c r="J67" s="85"/>
+      <c r="K67" s="85"/>
+      <c r="L67" s="85"/>
+      <c r="M67" s="85"/>
+      <c r="N67" s="85"/>
+      <c r="O67" s="85"/>
+      <c r="P67" s="85"/>
+      <c r="Q67" s="85"/>
+      <c r="R67" s="85"/>
+      <c r="S67" s="85"/>
+      <c r="T67" s="85"/>
+      <c r="U67" s="85"/>
+      <c r="V67" s="85"/>
+      <c r="W67" s="85"/>
+      <c r="X67" s="85"/>
+      <c r="Y67" s="85"/>
+      <c r="Z67" s="85"/>
+      <c r="AA67" s="85"/>
+      <c r="AB67" s="85"/>
+      <c r="AC67" s="85"/>
+      <c r="AD67" s="85"/>
+      <c r="AE67" s="85"/>
       <c r="AF67" s="2"/>
       <c r="AG67" s="2"/>
       <c r="AH67" s="2"/>
     </row>
-    <row r="68" ht="18.0" customHeight="1">
+    <row r="68" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -3753,7 +4170,7 @@
       <c r="AG68" s="2"/>
       <c r="AH68" s="2"/>
     </row>
-    <row r="69" ht="18.0" customHeight="1">
+    <row r="69" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3789,7 +4206,7 @@
       <c r="AG69" s="2"/>
       <c r="AH69" s="2"/>
     </row>
-    <row r="70" ht="18.0" customHeight="1">
+    <row r="70" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -3825,7 +4242,7 @@
       <c r="AG70" s="2"/>
       <c r="AH70" s="2"/>
     </row>
-    <row r="71" ht="18.0" customHeight="1">
+    <row r="71" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3861,7 +4278,7 @@
       <c r="AG71" s="2"/>
       <c r="AH71" s="2"/>
     </row>
-    <row r="72" ht="18.0" customHeight="1">
+    <row r="72" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3897,7 +4314,7 @@
       <c r="AG72" s="2"/>
       <c r="AH72" s="2"/>
     </row>
-    <row r="73" ht="18.0" customHeight="1">
+    <row r="73" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -3933,7 +4350,7 @@
       <c r="AG73" s="2"/>
       <c r="AH73" s="2"/>
     </row>
-    <row r="74" ht="18.0" customHeight="1">
+    <row r="74" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -3969,7 +4386,7 @@
       <c r="AG74" s="2"/>
       <c r="AH74" s="2"/>
     </row>
-    <row r="75" ht="18.0" customHeight="1">
+    <row r="75" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -4005,7 +4422,7 @@
       <c r="AG75" s="2"/>
       <c r="AH75" s="2"/>
     </row>
-    <row r="76" ht="18.0" customHeight="1">
+    <row r="76" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -4041,7 +4458,7 @@
       <c r="AG76" s="2"/>
       <c r="AH76" s="2"/>
     </row>
-    <row r="77" ht="18.0" customHeight="1">
+    <row r="77" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -4077,7 +4494,7 @@
       <c r="AG77" s="2"/>
       <c r="AH77" s="2"/>
     </row>
-    <row r="78" ht="18.0" customHeight="1">
+    <row r="78" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -4113,7 +4530,7 @@
       <c r="AG78" s="2"/>
       <c r="AH78" s="2"/>
     </row>
-    <row r="79" ht="18.0" customHeight="1">
+    <row r="79" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -4149,7 +4566,7 @@
       <c r="AG79" s="2"/>
       <c r="AH79" s="2"/>
     </row>
-    <row r="80" ht="18.0" customHeight="1">
+    <row r="80" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -4185,7 +4602,7 @@
       <c r="AG80" s="2"/>
       <c r="AH80" s="2"/>
     </row>
-    <row r="81" ht="18.0" customHeight="1">
+    <row r="81" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -4221,7 +4638,7 @@
       <c r="AG81" s="2"/>
       <c r="AH81" s="2"/>
     </row>
-    <row r="82" ht="18.0" customHeight="1">
+    <row r="82" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -4257,7 +4674,7 @@
       <c r="AG82" s="2"/>
       <c r="AH82" s="2"/>
     </row>
-    <row r="83" ht="18.0" customHeight="1">
+    <row r="83" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -4293,7 +4710,7 @@
       <c r="AG83" s="2"/>
       <c r="AH83" s="2"/>
     </row>
-    <row r="84" ht="18.0" customHeight="1">
+    <row r="84" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -4329,7 +4746,7 @@
       <c r="AG84" s="2"/>
       <c r="AH84" s="2"/>
     </row>
-    <row r="85" ht="18.0" customHeight="1">
+    <row r="85" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -4365,7 +4782,7 @@
       <c r="AG85" s="2"/>
       <c r="AH85" s="2"/>
     </row>
-    <row r="86" ht="18.0" customHeight="1">
+    <row r="86" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -4401,7 +4818,7 @@
       <c r="AG86" s="2"/>
       <c r="AH86" s="2"/>
     </row>
-    <row r="87" ht="18.0" customHeight="1">
+    <row r="87" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -4437,7 +4854,7 @@
       <c r="AG87" s="2"/>
       <c r="AH87" s="2"/>
     </row>
-    <row r="88" ht="18.0" customHeight="1">
+    <row r="88" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -4473,7 +4890,7 @@
       <c r="AG88" s="2"/>
       <c r="AH88" s="2"/>
     </row>
-    <row r="89" ht="18.0" customHeight="1">
+    <row r="89" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -4509,7 +4926,7 @@
       <c r="AG89" s="2"/>
       <c r="AH89" s="2"/>
     </row>
-    <row r="90" ht="18.0" customHeight="1">
+    <row r="90" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -4545,7 +4962,7 @@
       <c r="AG90" s="2"/>
       <c r="AH90" s="2"/>
     </row>
-    <row r="91" ht="18.0" customHeight="1">
+    <row r="91" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -4581,7 +4998,7 @@
       <c r="AG91" s="2"/>
       <c r="AH91" s="2"/>
     </row>
-    <row r="92" ht="18.0" customHeight="1">
+    <row r="92" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -4617,7 +5034,7 @@
       <c r="AG92" s="2"/>
       <c r="AH92" s="2"/>
     </row>
-    <row r="93" ht="18.0" customHeight="1">
+    <row r="93" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -4653,7 +5070,7 @@
       <c r="AG93" s="2"/>
       <c r="AH93" s="2"/>
     </row>
-    <row r="94" ht="18.0" customHeight="1">
+    <row r="94" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -4689,7 +5106,7 @@
       <c r="AG94" s="2"/>
       <c r="AH94" s="2"/>
     </row>
-    <row r="95" ht="18.0" customHeight="1">
+    <row r="95" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -4725,7 +5142,7 @@
       <c r="AG95" s="2"/>
       <c r="AH95" s="2"/>
     </row>
-    <row r="96" ht="18.0" customHeight="1">
+    <row r="96" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -4761,7 +5178,7 @@
       <c r="AG96" s="2"/>
       <c r="AH96" s="2"/>
     </row>
-    <row r="97" ht="18.0" customHeight="1">
+    <row r="97" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -4797,7 +5214,7 @@
       <c r="AG97" s="2"/>
       <c r="AH97" s="2"/>
     </row>
-    <row r="98" ht="18.0" customHeight="1">
+    <row r="98" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -4833,7 +5250,7 @@
       <c r="AG98" s="2"/>
       <c r="AH98" s="2"/>
     </row>
-    <row r="99" ht="18.0" customHeight="1">
+    <row r="99" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -4869,7 +5286,7 @@
       <c r="AG99" s="2"/>
       <c r="AH99" s="2"/>
     </row>
-    <row r="100" ht="18.0" customHeight="1">
+    <row r="100" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -4905,7 +5322,7 @@
       <c r="AG100" s="2"/>
       <c r="AH100" s="2"/>
     </row>
-    <row r="101" ht="18.0" customHeight="1">
+    <row r="101" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -4941,7 +5358,7 @@
       <c r="AG101" s="2"/>
       <c r="AH101" s="2"/>
     </row>
-    <row r="102" ht="18.0" customHeight="1">
+    <row r="102" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -4977,7 +5394,7 @@
       <c r="AG102" s="2"/>
       <c r="AH102" s="2"/>
     </row>
-    <row r="103" ht="18.0" customHeight="1">
+    <row r="103" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -5013,7 +5430,7 @@
       <c r="AG103" s="2"/>
       <c r="AH103" s="2"/>
     </row>
-    <row r="104" ht="18.0" customHeight="1">
+    <row r="104" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -5049,7 +5466,7 @@
       <c r="AG104" s="2"/>
       <c r="AH104" s="2"/>
     </row>
-    <row r="105" ht="18.0" customHeight="1">
+    <row r="105" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -5085,7 +5502,7 @@
       <c r="AG105" s="2"/>
       <c r="AH105" s="2"/>
     </row>
-    <row r="106" ht="18.0" customHeight="1">
+    <row r="106" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -5121,7 +5538,7 @@
       <c r="AG106" s="2"/>
       <c r="AH106" s="2"/>
     </row>
-    <row r="107" ht="18.0" customHeight="1">
+    <row r="107" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -5157,7 +5574,7 @@
       <c r="AG107" s="2"/>
       <c r="AH107" s="2"/>
     </row>
-    <row r="108" ht="18.0" customHeight="1">
+    <row r="108" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -5193,7 +5610,7 @@
       <c r="AG108" s="2"/>
       <c r="AH108" s="2"/>
     </row>
-    <row r="109" ht="18.0" customHeight="1">
+    <row r="109" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -5229,7 +5646,7 @@
       <c r="AG109" s="2"/>
       <c r="AH109" s="2"/>
     </row>
-    <row r="110" ht="18.0" customHeight="1">
+    <row r="110" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -5265,7 +5682,7 @@
       <c r="AG110" s="2"/>
       <c r="AH110" s="2"/>
     </row>
-    <row r="111" ht="18.0" customHeight="1">
+    <row r="111" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -5301,7 +5718,7 @@
       <c r="AG111" s="2"/>
       <c r="AH111" s="2"/>
     </row>
-    <row r="112" ht="18.0" customHeight="1">
+    <row r="112" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -5337,7 +5754,7 @@
       <c r="AG112" s="2"/>
       <c r="AH112" s="2"/>
     </row>
-    <row r="113" ht="18.0" customHeight="1">
+    <row r="113" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -5373,7 +5790,7 @@
       <c r="AG113" s="2"/>
       <c r="AH113" s="2"/>
     </row>
-    <row r="114" ht="18.0" customHeight="1">
+    <row r="114" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -5409,7 +5826,7 @@
       <c r="AG114" s="2"/>
       <c r="AH114" s="2"/>
     </row>
-    <row r="115" ht="18.0" customHeight="1">
+    <row r="115" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -5445,7 +5862,7 @@
       <c r="AG115" s="2"/>
       <c r="AH115" s="2"/>
     </row>
-    <row r="116" ht="18.0" customHeight="1">
+    <row r="116" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -5481,7 +5898,7 @@
       <c r="AG116" s="2"/>
       <c r="AH116" s="2"/>
     </row>
-    <row r="117" ht="18.0" customHeight="1">
+    <row r="117" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -5517,7 +5934,7 @@
       <c r="AG117" s="2"/>
       <c r="AH117" s="2"/>
     </row>
-    <row r="118" ht="18.0" customHeight="1">
+    <row r="118" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -5553,7 +5970,7 @@
       <c r="AG118" s="2"/>
       <c r="AH118" s="2"/>
     </row>
-    <row r="119" ht="18.0" customHeight="1">
+    <row r="119" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -5589,7 +6006,7 @@
       <c r="AG119" s="2"/>
       <c r="AH119" s="2"/>
     </row>
-    <row r="120" ht="18.0" customHeight="1">
+    <row r="120" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -5625,7 +6042,7 @@
       <c r="AG120" s="2"/>
       <c r="AH120" s="2"/>
     </row>
-    <row r="121" ht="18.0" customHeight="1">
+    <row r="121" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -5661,7 +6078,7 @@
       <c r="AG121" s="2"/>
       <c r="AH121" s="2"/>
     </row>
-    <row r="122" ht="18.0" customHeight="1">
+    <row r="122" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -5697,7 +6114,7 @@
       <c r="AG122" s="2"/>
       <c r="AH122" s="2"/>
     </row>
-    <row r="123" ht="18.0" customHeight="1">
+    <row r="123" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -5733,7 +6150,7 @@
       <c r="AG123" s="2"/>
       <c r="AH123" s="2"/>
     </row>
-    <row r="124" ht="18.0" customHeight="1">
+    <row r="124" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -5769,7 +6186,7 @@
       <c r="AG124" s="2"/>
       <c r="AH124" s="2"/>
     </row>
-    <row r="125" ht="18.0" customHeight="1">
+    <row r="125" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -5805,7 +6222,7 @@
       <c r="AG125" s="2"/>
       <c r="AH125" s="2"/>
     </row>
-    <row r="126" ht="18.0" customHeight="1">
+    <row r="126" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -5841,7 +6258,7 @@
       <c r="AG126" s="2"/>
       <c r="AH126" s="2"/>
     </row>
-    <row r="127" ht="18.0" customHeight="1">
+    <row r="127" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -5877,7 +6294,7 @@
       <c r="AG127" s="2"/>
       <c r="AH127" s="2"/>
     </row>
-    <row r="128" ht="18.0" customHeight="1">
+    <row r="128" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -5913,7 +6330,7 @@
       <c r="AG128" s="2"/>
       <c r="AH128" s="2"/>
     </row>
-    <row r="129" ht="18.0" customHeight="1">
+    <row r="129" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -5949,7 +6366,7 @@
       <c r="AG129" s="2"/>
       <c r="AH129" s="2"/>
     </row>
-    <row r="130" ht="18.0" customHeight="1">
+    <row r="130" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -5985,7 +6402,7 @@
       <c r="AG130" s="2"/>
       <c r="AH130" s="2"/>
     </row>
-    <row r="131" ht="18.0" customHeight="1">
+    <row r="131" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -6021,7 +6438,7 @@
       <c r="AG131" s="2"/>
       <c r="AH131" s="2"/>
     </row>
-    <row r="132" ht="18.0" customHeight="1">
+    <row r="132" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -6057,7 +6474,7 @@
       <c r="AG132" s="2"/>
       <c r="AH132" s="2"/>
     </row>
-    <row r="133" ht="18.0" customHeight="1">
+    <row r="133" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -6093,7 +6510,7 @@
       <c r="AG133" s="2"/>
       <c r="AH133" s="2"/>
     </row>
-    <row r="134" ht="18.0" customHeight="1">
+    <row r="134" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -6129,7 +6546,7 @@
       <c r="AG134" s="2"/>
       <c r="AH134" s="2"/>
     </row>
-    <row r="135" ht="18.0" customHeight="1">
+    <row r="135" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -6165,7 +6582,7 @@
       <c r="AG135" s="2"/>
       <c r="AH135" s="2"/>
     </row>
-    <row r="136" ht="18.0" customHeight="1">
+    <row r="136" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -6201,7 +6618,7 @@
       <c r="AG136" s="2"/>
       <c r="AH136" s="2"/>
     </row>
-    <row r="137" ht="18.0" customHeight="1">
+    <row r="137" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -6237,7 +6654,7 @@
       <c r="AG137" s="2"/>
       <c r="AH137" s="2"/>
     </row>
-    <row r="138" ht="18.0" customHeight="1">
+    <row r="138" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -6273,7 +6690,7 @@
       <c r="AG138" s="2"/>
       <c r="AH138" s="2"/>
     </row>
-    <row r="139" ht="18.0" customHeight="1">
+    <row r="139" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -6309,7 +6726,7 @@
       <c r="AG139" s="2"/>
       <c r="AH139" s="2"/>
     </row>
-    <row r="140" ht="18.0" customHeight="1">
+    <row r="140" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -6345,7 +6762,7 @@
       <c r="AG140" s="2"/>
       <c r="AH140" s="2"/>
     </row>
-    <row r="141" ht="18.0" customHeight="1">
+    <row r="141" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -6381,7 +6798,7 @@
       <c r="AG141" s="2"/>
       <c r="AH141" s="2"/>
     </row>
-    <row r="142" ht="18.0" customHeight="1">
+    <row r="142" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -6417,7 +6834,7 @@
       <c r="AG142" s="2"/>
       <c r="AH142" s="2"/>
     </row>
-    <row r="143" ht="18.0" customHeight="1">
+    <row r="143" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -6453,7 +6870,7 @@
       <c r="AG143" s="2"/>
       <c r="AH143" s="2"/>
     </row>
-    <row r="144" ht="18.0" customHeight="1">
+    <row r="144" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -6489,7 +6906,7 @@
       <c r="AG144" s="2"/>
       <c r="AH144" s="2"/>
     </row>
-    <row r="145" ht="18.0" customHeight="1">
+    <row r="145" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -6525,7 +6942,7 @@
       <c r="AG145" s="2"/>
       <c r="AH145" s="2"/>
     </row>
-    <row r="146" ht="18.0" customHeight="1">
+    <row r="146" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -6561,7 +6978,7 @@
       <c r="AG146" s="2"/>
       <c r="AH146" s="2"/>
     </row>
-    <row r="147" ht="18.0" customHeight="1">
+    <row r="147" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -6597,7 +7014,7 @@
       <c r="AG147" s="2"/>
       <c r="AH147" s="2"/>
     </row>
-    <row r="148" ht="18.0" customHeight="1">
+    <row r="148" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -6633,7 +7050,7 @@
       <c r="AG148" s="2"/>
       <c r="AH148" s="2"/>
     </row>
-    <row r="149" ht="18.0" customHeight="1">
+    <row r="149" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -6669,7 +7086,7 @@
       <c r="AG149" s="2"/>
       <c r="AH149" s="2"/>
     </row>
-    <row r="150" ht="18.0" customHeight="1">
+    <row r="150" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -6705,7 +7122,7 @@
       <c r="AG150" s="2"/>
       <c r="AH150" s="2"/>
     </row>
-    <row r="151" ht="18.0" customHeight="1">
+    <row r="151" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -6741,7 +7158,7 @@
       <c r="AG151" s="2"/>
       <c r="AH151" s="2"/>
     </row>
-    <row r="152" ht="18.0" customHeight="1">
+    <row r="152" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -6777,7 +7194,7 @@
       <c r="AG152" s="2"/>
       <c r="AH152" s="2"/>
     </row>
-    <row r="153" ht="18.0" customHeight="1">
+    <row r="153" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -6813,7 +7230,7 @@
       <c r="AG153" s="2"/>
       <c r="AH153" s="2"/>
     </row>
-    <row r="154" ht="18.0" customHeight="1">
+    <row r="154" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -6849,7 +7266,7 @@
       <c r="AG154" s="2"/>
       <c r="AH154" s="2"/>
     </row>
-    <row r="155" ht="18.0" customHeight="1">
+    <row r="155" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -6885,7 +7302,7 @@
       <c r="AG155" s="2"/>
       <c r="AH155" s="2"/>
     </row>
-    <row r="156" ht="18.0" customHeight="1">
+    <row r="156" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -6921,7 +7338,7 @@
       <c r="AG156" s="2"/>
       <c r="AH156" s="2"/>
     </row>
-    <row r="157" ht="18.0" customHeight="1">
+    <row r="157" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -6957,7 +7374,7 @@
       <c r="AG157" s="2"/>
       <c r="AH157" s="2"/>
     </row>
-    <row r="158" ht="18.0" customHeight="1">
+    <row r="158" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -6993,7 +7410,7 @@
       <c r="AG158" s="2"/>
       <c r="AH158" s="2"/>
     </row>
-    <row r="159" ht="18.0" customHeight="1">
+    <row r="159" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -7029,7 +7446,7 @@
       <c r="AG159" s="2"/>
       <c r="AH159" s="2"/>
     </row>
-    <row r="160" ht="18.0" customHeight="1">
+    <row r="160" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -7065,7 +7482,7 @@
       <c r="AG160" s="2"/>
       <c r="AH160" s="2"/>
     </row>
-    <row r="161" ht="18.0" customHeight="1">
+    <row r="161" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -7101,7 +7518,7 @@
       <c r="AG161" s="2"/>
       <c r="AH161" s="2"/>
     </row>
-    <row r="162" ht="18.0" customHeight="1">
+    <row r="162" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -7137,7 +7554,7 @@
       <c r="AG162" s="2"/>
       <c r="AH162" s="2"/>
     </row>
-    <row r="163" ht="18.0" customHeight="1">
+    <row r="163" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -7173,7 +7590,7 @@
       <c r="AG163" s="2"/>
       <c r="AH163" s="2"/>
     </row>
-    <row r="164" ht="18.0" customHeight="1">
+    <row r="164" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -7209,7 +7626,7 @@
       <c r="AG164" s="2"/>
       <c r="AH164" s="2"/>
     </row>
-    <row r="165" ht="18.0" customHeight="1">
+    <row r="165" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -7245,7 +7662,7 @@
       <c r="AG165" s="2"/>
       <c r="AH165" s="2"/>
     </row>
-    <row r="166" ht="18.0" customHeight="1">
+    <row r="166" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -7281,7 +7698,7 @@
       <c r="AG166" s="2"/>
       <c r="AH166" s="2"/>
     </row>
-    <row r="167" ht="18.0" customHeight="1">
+    <row r="167" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -7317,7 +7734,7 @@
       <c r="AG167" s="2"/>
       <c r="AH167" s="2"/>
     </row>
-    <row r="168" ht="18.0" customHeight="1">
+    <row r="168" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -7353,7 +7770,7 @@
       <c r="AG168" s="2"/>
       <c r="AH168" s="2"/>
     </row>
-    <row r="169" ht="18.0" customHeight="1">
+    <row r="169" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -7389,7 +7806,7 @@
       <c r="AG169" s="2"/>
       <c r="AH169" s="2"/>
     </row>
-    <row r="170" ht="18.0" customHeight="1">
+    <row r="170" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -7425,7 +7842,7 @@
       <c r="AG170" s="2"/>
       <c r="AH170" s="2"/>
     </row>
-    <row r="171" ht="18.0" customHeight="1">
+    <row r="171" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -7461,7 +7878,7 @@
       <c r="AG171" s="2"/>
       <c r="AH171" s="2"/>
     </row>
-    <row r="172" ht="18.0" customHeight="1">
+    <row r="172" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -7497,7 +7914,7 @@
       <c r="AG172" s="2"/>
       <c r="AH172" s="2"/>
     </row>
-    <row r="173" ht="18.0" customHeight="1">
+    <row r="173" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -7533,7 +7950,7 @@
       <c r="AG173" s="2"/>
       <c r="AH173" s="2"/>
     </row>
-    <row r="174" ht="18.0" customHeight="1">
+    <row r="174" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -7569,7 +7986,7 @@
       <c r="AG174" s="2"/>
       <c r="AH174" s="2"/>
     </row>
-    <row r="175" ht="18.0" customHeight="1">
+    <row r="175" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -7605,7 +8022,7 @@
       <c r="AG175" s="2"/>
       <c r="AH175" s="2"/>
     </row>
-    <row r="176" ht="18.0" customHeight="1">
+    <row r="176" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -7641,7 +8058,7 @@
       <c r="AG176" s="2"/>
       <c r="AH176" s="2"/>
     </row>
-    <row r="177" ht="18.0" customHeight="1">
+    <row r="177" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -7677,7 +8094,7 @@
       <c r="AG177" s="2"/>
       <c r="AH177" s="2"/>
     </row>
-    <row r="178" ht="18.0" customHeight="1">
+    <row r="178" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -7713,7 +8130,7 @@
       <c r="AG178" s="2"/>
       <c r="AH178" s="2"/>
     </row>
-    <row r="179" ht="18.0" customHeight="1">
+    <row r="179" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -7749,7 +8166,7 @@
       <c r="AG179" s="2"/>
       <c r="AH179" s="2"/>
     </row>
-    <row r="180" ht="18.0" customHeight="1">
+    <row r="180" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -7785,7 +8202,7 @@
       <c r="AG180" s="2"/>
       <c r="AH180" s="2"/>
     </row>
-    <row r="181" ht="18.0" customHeight="1">
+    <row r="181" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -7821,7 +8238,7 @@
       <c r="AG181" s="2"/>
       <c r="AH181" s="2"/>
     </row>
-    <row r="182" ht="18.0" customHeight="1">
+    <row r="182" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -7857,7 +8274,7 @@
       <c r="AG182" s="2"/>
       <c r="AH182" s="2"/>
     </row>
-    <row r="183" ht="18.0" customHeight="1">
+    <row r="183" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -7893,7 +8310,7 @@
       <c r="AG183" s="2"/>
       <c r="AH183" s="2"/>
     </row>
-    <row r="184" ht="18.0" customHeight="1">
+    <row r="184" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -7929,7 +8346,7 @@
       <c r="AG184" s="2"/>
       <c r="AH184" s="2"/>
     </row>
-    <row r="185" ht="18.0" customHeight="1">
+    <row r="185" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -7965,7 +8382,7 @@
       <c r="AG185" s="2"/>
       <c r="AH185" s="2"/>
     </row>
-    <row r="186" ht="18.0" customHeight="1">
+    <row r="186" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -8001,7 +8418,7 @@
       <c r="AG186" s="2"/>
       <c r="AH186" s="2"/>
     </row>
-    <row r="187" ht="18.0" customHeight="1">
+    <row r="187" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -8037,7 +8454,7 @@
       <c r="AG187" s="2"/>
       <c r="AH187" s="2"/>
     </row>
-    <row r="188" ht="18.0" customHeight="1">
+    <row r="188" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -8073,7 +8490,7 @@
       <c r="AG188" s="2"/>
       <c r="AH188" s="2"/>
     </row>
-    <row r="189" ht="18.0" customHeight="1">
+    <row r="189" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -8109,7 +8526,7 @@
       <c r="AG189" s="2"/>
       <c r="AH189" s="2"/>
     </row>
-    <row r="190" ht="18.0" customHeight="1">
+    <row r="190" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -8145,7 +8562,7 @@
       <c r="AG190" s="2"/>
       <c r="AH190" s="2"/>
     </row>
-    <row r="191" ht="18.0" customHeight="1">
+    <row r="191" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -8181,7 +8598,7 @@
       <c r="AG191" s="2"/>
       <c r="AH191" s="2"/>
     </row>
-    <row r="192" ht="18.0" customHeight="1">
+    <row r="192" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -8217,7 +8634,7 @@
       <c r="AG192" s="2"/>
       <c r="AH192" s="2"/>
     </row>
-    <row r="193" ht="18.0" customHeight="1">
+    <row r="193" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -8253,7 +8670,7 @@
       <c r="AG193" s="2"/>
       <c r="AH193" s="2"/>
     </row>
-    <row r="194" ht="18.0" customHeight="1">
+    <row r="194" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -8289,7 +8706,7 @@
       <c r="AG194" s="2"/>
       <c r="AH194" s="2"/>
     </row>
-    <row r="195" ht="18.0" customHeight="1">
+    <row r="195" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -8325,7 +8742,7 @@
       <c r="AG195" s="2"/>
       <c r="AH195" s="2"/>
     </row>
-    <row r="196" ht="18.0" customHeight="1">
+    <row r="196" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -8361,7 +8778,7 @@
       <c r="AG196" s="2"/>
       <c r="AH196" s="2"/>
     </row>
-    <row r="197" ht="18.0" customHeight="1">
+    <row r="197" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -8397,7 +8814,7 @@
       <c r="AG197" s="2"/>
       <c r="AH197" s="2"/>
     </row>
-    <row r="198" ht="18.0" customHeight="1">
+    <row r="198" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -8433,7 +8850,7 @@
       <c r="AG198" s="2"/>
       <c r="AH198" s="2"/>
     </row>
-    <row r="199" ht="18.0" customHeight="1">
+    <row r="199" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -8469,7 +8886,7 @@
       <c r="AG199" s="2"/>
       <c r="AH199" s="2"/>
     </row>
-    <row r="200" ht="18.0" customHeight="1">
+    <row r="200" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -8505,7 +8922,7 @@
       <c r="AG200" s="2"/>
       <c r="AH200" s="2"/>
     </row>
-    <row r="201" ht="18.0" customHeight="1">
+    <row r="201" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -8541,7 +8958,7 @@
       <c r="AG201" s="2"/>
       <c r="AH201" s="2"/>
     </row>
-    <row r="202" ht="18.0" customHeight="1">
+    <row r="202" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -8577,7 +8994,7 @@
       <c r="AG202" s="2"/>
       <c r="AH202" s="2"/>
     </row>
-    <row r="203" ht="18.0" customHeight="1">
+    <row r="203" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -8613,7 +9030,7 @@
       <c r="AG203" s="2"/>
       <c r="AH203" s="2"/>
     </row>
-    <row r="204" ht="18.0" customHeight="1">
+    <row r="204" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -8649,7 +9066,7 @@
       <c r="AG204" s="2"/>
       <c r="AH204" s="2"/>
     </row>
-    <row r="205" ht="18.0" customHeight="1">
+    <row r="205" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -8685,7 +9102,7 @@
       <c r="AG205" s="2"/>
       <c r="AH205" s="2"/>
     </row>
-    <row r="206" ht="18.0" customHeight="1">
+    <row r="206" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -8721,7 +9138,7 @@
       <c r="AG206" s="2"/>
       <c r="AH206" s="2"/>
     </row>
-    <row r="207" ht="18.0" customHeight="1">
+    <row r="207" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -8757,7 +9174,7 @@
       <c r="AG207" s="2"/>
       <c r="AH207" s="2"/>
     </row>
-    <row r="208" ht="18.0" customHeight="1">
+    <row r="208" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -8793,7 +9210,7 @@
       <c r="AG208" s="2"/>
       <c r="AH208" s="2"/>
     </row>
-    <row r="209" ht="18.0" customHeight="1">
+    <row r="209" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -8829,7 +9246,7 @@
       <c r="AG209" s="2"/>
       <c r="AH209" s="2"/>
     </row>
-    <row r="210" ht="18.0" customHeight="1">
+    <row r="210" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -8865,7 +9282,7 @@
       <c r="AG210" s="2"/>
       <c r="AH210" s="2"/>
     </row>
-    <row r="211" ht="18.0" customHeight="1">
+    <row r="211" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -8901,7 +9318,7 @@
       <c r="AG211" s="2"/>
       <c r="AH211" s="2"/>
     </row>
-    <row r="212" ht="18.0" customHeight="1">
+    <row r="212" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -8937,7 +9354,7 @@
       <c r="AG212" s="2"/>
       <c r="AH212" s="2"/>
     </row>
-    <row r="213" ht="18.0" customHeight="1">
+    <row r="213" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -8973,7 +9390,7 @@
       <c r="AG213" s="2"/>
       <c r="AH213" s="2"/>
     </row>
-    <row r="214" ht="18.0" customHeight="1">
+    <row r="214" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -9009,7 +9426,7 @@
       <c r="AG214" s="2"/>
       <c r="AH214" s="2"/>
     </row>
-    <row r="215" ht="18.0" customHeight="1">
+    <row r="215" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -9045,7 +9462,7 @@
       <c r="AG215" s="2"/>
       <c r="AH215" s="2"/>
     </row>
-    <row r="216" ht="18.0" customHeight="1">
+    <row r="216" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -9081,7 +9498,7 @@
       <c r="AG216" s="2"/>
       <c r="AH216" s="2"/>
     </row>
-    <row r="217" ht="18.0" customHeight="1">
+    <row r="217" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -9117,7 +9534,7 @@
       <c r="AG217" s="2"/>
       <c r="AH217" s="2"/>
     </row>
-    <row r="218" ht="18.0" customHeight="1">
+    <row r="218" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -9153,7 +9570,7 @@
       <c r="AG218" s="2"/>
       <c r="AH218" s="2"/>
     </row>
-    <row r="219" ht="18.0" customHeight="1">
+    <row r="219" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -9189,7 +9606,7 @@
       <c r="AG219" s="2"/>
       <c r="AH219" s="2"/>
     </row>
-    <row r="220" ht="18.0" customHeight="1">
+    <row r="220" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -9225,7 +9642,7 @@
       <c r="AG220" s="2"/>
       <c r="AH220" s="2"/>
     </row>
-    <row r="221" ht="18.0" customHeight="1">
+    <row r="221" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -9261,7 +9678,7 @@
       <c r="AG221" s="2"/>
       <c r="AH221" s="2"/>
     </row>
-    <row r="222" ht="18.0" customHeight="1">
+    <row r="222" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -9297,7 +9714,7 @@
       <c r="AG222" s="2"/>
       <c r="AH222" s="2"/>
     </row>
-    <row r="223" ht="18.0" customHeight="1">
+    <row r="223" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -9333,7 +9750,7 @@
       <c r="AG223" s="2"/>
       <c r="AH223" s="2"/>
     </row>
-    <row r="224" ht="18.0" customHeight="1">
+    <row r="224" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -9369,7 +9786,7 @@
       <c r="AG224" s="2"/>
       <c r="AH224" s="2"/>
     </row>
-    <row r="225" ht="18.0" customHeight="1">
+    <row r="225" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -9405,7 +9822,7 @@
       <c r="AG225" s="2"/>
       <c r="AH225" s="2"/>
     </row>
-    <row r="226" ht="18.0" customHeight="1">
+    <row r="226" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -9441,7 +9858,7 @@
       <c r="AG226" s="2"/>
       <c r="AH226" s="2"/>
     </row>
-    <row r="227" ht="18.0" customHeight="1">
+    <row r="227" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -9477,7 +9894,7 @@
       <c r="AG227" s="2"/>
       <c r="AH227" s="2"/>
     </row>
-    <row r="228" ht="18.0" customHeight="1">
+    <row r="228" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -9513,7 +9930,7 @@
       <c r="AG228" s="2"/>
       <c r="AH228" s="2"/>
     </row>
-    <row r="229" ht="18.0" customHeight="1">
+    <row r="229" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -9549,7 +9966,7 @@
       <c r="AG229" s="2"/>
       <c r="AH229" s="2"/>
     </row>
-    <row r="230" ht="18.0" customHeight="1">
+    <row r="230" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -9585,7 +10002,7 @@
       <c r="AG230" s="2"/>
       <c r="AH230" s="2"/>
     </row>
-    <row r="231" ht="18.0" customHeight="1">
+    <row r="231" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -9621,7 +10038,7 @@
       <c r="AG231" s="2"/>
       <c r="AH231" s="2"/>
     </row>
-    <row r="232" ht="18.0" customHeight="1">
+    <row r="232" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -9657,7 +10074,7 @@
       <c r="AG232" s="2"/>
       <c r="AH232" s="2"/>
     </row>
-    <row r="233" ht="18.0" customHeight="1">
+    <row r="233" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -9693,7 +10110,7 @@
       <c r="AG233" s="2"/>
       <c r="AH233" s="2"/>
     </row>
-    <row r="234" ht="18.0" customHeight="1">
+    <row r="234" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -9729,7 +10146,7 @@
       <c r="AG234" s="2"/>
       <c r="AH234" s="2"/>
     </row>
-    <row r="235" ht="18.0" customHeight="1">
+    <row r="235" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -9765,7 +10182,7 @@
       <c r="AG235" s="2"/>
       <c r="AH235" s="2"/>
     </row>
-    <row r="236" ht="18.0" customHeight="1">
+    <row r="236" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -9801,7 +10218,7 @@
       <c r="AG236" s="2"/>
       <c r="AH236" s="2"/>
     </row>
-    <row r="237" ht="18.0" customHeight="1">
+    <row r="237" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -9837,7 +10254,7 @@
       <c r="AG237" s="2"/>
       <c r="AH237" s="2"/>
     </row>
-    <row r="238" ht="18.0" customHeight="1">
+    <row r="238" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -9873,7 +10290,7 @@
       <c r="AG238" s="2"/>
       <c r="AH238" s="2"/>
     </row>
-    <row r="239" ht="18.0" customHeight="1">
+    <row r="239" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -9909,7 +10326,7 @@
       <c r="AG239" s="2"/>
       <c r="AH239" s="2"/>
     </row>
-    <row r="240" ht="18.0" customHeight="1">
+    <row r="240" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -9945,7 +10362,7 @@
       <c r="AG240" s="2"/>
       <c r="AH240" s="2"/>
     </row>
-    <row r="241" ht="18.0" customHeight="1">
+    <row r="241" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -9981,7 +10398,7 @@
       <c r="AG241" s="2"/>
       <c r="AH241" s="2"/>
     </row>
-    <row r="242" ht="18.0" customHeight="1">
+    <row r="242" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -10017,7 +10434,7 @@
       <c r="AG242" s="2"/>
       <c r="AH242" s="2"/>
     </row>
-    <row r="243" ht="18.0" customHeight="1">
+    <row r="243" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -10053,7 +10470,7 @@
       <c r="AG243" s="2"/>
       <c r="AH243" s="2"/>
     </row>
-    <row r="244" ht="18.0" customHeight="1">
+    <row r="244" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -10089,7 +10506,7 @@
       <c r="AG244" s="2"/>
       <c r="AH244" s="2"/>
     </row>
-    <row r="245" ht="18.0" customHeight="1">
+    <row r="245" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -10125,7 +10542,7 @@
       <c r="AG245" s="2"/>
       <c r="AH245" s="2"/>
     </row>
-    <row r="246" ht="18.0" customHeight="1">
+    <row r="246" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -10161,7 +10578,7 @@
       <c r="AG246" s="2"/>
       <c r="AH246" s="2"/>
     </row>
-    <row r="247" ht="18.0" customHeight="1">
+    <row r="247" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -10197,7 +10614,7 @@
       <c r="AG247" s="2"/>
       <c r="AH247" s="2"/>
     </row>
-    <row r="248" ht="18.0" customHeight="1">
+    <row r="248" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -10233,7 +10650,7 @@
       <c r="AG248" s="2"/>
       <c r="AH248" s="2"/>
     </row>
-    <row r="249" ht="18.0" customHeight="1">
+    <row r="249" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -10269,7 +10686,7 @@
       <c r="AG249" s="2"/>
       <c r="AH249" s="2"/>
     </row>
-    <row r="250" ht="18.0" customHeight="1">
+    <row r="250" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -10305,7 +10722,7 @@
       <c r="AG250" s="2"/>
       <c r="AH250" s="2"/>
     </row>
-    <row r="251" ht="18.0" customHeight="1">
+    <row r="251" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -10341,7 +10758,7 @@
       <c r="AG251" s="2"/>
       <c r="AH251" s="2"/>
     </row>
-    <row r="252" ht="18.0" customHeight="1">
+    <row r="252" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -10377,7 +10794,7 @@
       <c r="AG252" s="2"/>
       <c r="AH252" s="2"/>
     </row>
-    <row r="253" ht="18.0" customHeight="1">
+    <row r="253" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -10413,7 +10830,7 @@
       <c r="AG253" s="2"/>
       <c r="AH253" s="2"/>
     </row>
-    <row r="254" ht="18.0" customHeight="1">
+    <row r="254" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -10449,7 +10866,7 @@
       <c r="AG254" s="2"/>
       <c r="AH254" s="2"/>
     </row>
-    <row r="255" ht="18.0" customHeight="1">
+    <row r="255" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -10485,7 +10902,7 @@
       <c r="AG255" s="2"/>
       <c r="AH255" s="2"/>
     </row>
-    <row r="256" ht="18.0" customHeight="1">
+    <row r="256" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -10521,7 +10938,7 @@
       <c r="AG256" s="2"/>
       <c r="AH256" s="2"/>
     </row>
-    <row r="257" ht="18.0" customHeight="1">
+    <row r="257" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -10557,7 +10974,7 @@
       <c r="AG257" s="2"/>
       <c r="AH257" s="2"/>
     </row>
-    <row r="258" ht="18.0" customHeight="1">
+    <row r="258" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -10593,7 +11010,7 @@
       <c r="AG258" s="2"/>
       <c r="AH258" s="2"/>
     </row>
-    <row r="259" ht="18.0" customHeight="1">
+    <row r="259" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -10629,7 +11046,7 @@
       <c r="AG259" s="2"/>
       <c r="AH259" s="2"/>
     </row>
-    <row r="260" ht="18.0" customHeight="1">
+    <row r="260" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -10665,7 +11082,7 @@
       <c r="AG260" s="2"/>
       <c r="AH260" s="2"/>
     </row>
-    <row r="261" ht="18.0" customHeight="1">
+    <row r="261" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -10701,7 +11118,7 @@
       <c r="AG261" s="2"/>
       <c r="AH261" s="2"/>
     </row>
-    <row r="262" ht="18.0" customHeight="1">
+    <row r="262" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -10737,7 +11154,7 @@
       <c r="AG262" s="2"/>
       <c r="AH262" s="2"/>
     </row>
-    <row r="263" ht="18.0" customHeight="1">
+    <row r="263" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -10773,7 +11190,7 @@
       <c r="AG263" s="2"/>
       <c r="AH263" s="2"/>
     </row>
-    <row r="264" ht="18.0" customHeight="1">
+    <row r="264" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -10809,7 +11226,7 @@
       <c r="AG264" s="2"/>
       <c r="AH264" s="2"/>
     </row>
-    <row r="265" ht="18.0" customHeight="1">
+    <row r="265" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -10845,876 +11262,755 @@
       <c r="AG265" s="2"/>
       <c r="AH265" s="2"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="266" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="267" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="268" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="269" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="270" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="271" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="272" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="172">
-    <mergeCell ref="Q20:X20"/>
-    <mergeCell ref="Y20:AC20"/>
-    <mergeCell ref="Q21:X21"/>
-    <mergeCell ref="Y21:AC21"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="Q22:X22"/>
-    <mergeCell ref="Y22:AC22"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="AE1:AE2"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="I2:W5"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="X6:AB6"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="J7:W8"/>
-    <mergeCell ref="J9:W9"/>
-    <mergeCell ref="J10:W10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:W11"/>
-    <mergeCell ref="K12:AC12"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="J13:AC15"/>
-    <mergeCell ref="A16:AE16"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="O17:AE17"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:X18"/>
-    <mergeCell ref="Y18:AC18"/>
-    <mergeCell ref="AD18:AE18"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:X19"/>
-    <mergeCell ref="Y19:AC19"/>
-    <mergeCell ref="AD19:AE19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A13:I15"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="Q23:X23"/>
-    <mergeCell ref="Y23:AC23"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q32:X32"/>
-    <mergeCell ref="Q33:X33"/>
-    <mergeCell ref="Y33:AC33"/>
-    <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="Q30:X30"/>
-    <mergeCell ref="Y30:AC30"/>
-    <mergeCell ref="Q31:X31"/>
-    <mergeCell ref="Y31:AC31"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="Y32:AC32"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="N57:P64"/>
-    <mergeCell ref="Q57:S64"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="Q34:X34"/>
-    <mergeCell ref="Y34:AC34"/>
-    <mergeCell ref="AD34:AE34"/>
-    <mergeCell ref="Y35:AC35"/>
-    <mergeCell ref="AD35:AE35"/>
-    <mergeCell ref="Q35:X35"/>
-    <mergeCell ref="Q36:X36"/>
-    <mergeCell ref="Y36:AC36"/>
-    <mergeCell ref="AD36:AE36"/>
-    <mergeCell ref="Q37:X37"/>
-    <mergeCell ref="Y37:AC37"/>
-    <mergeCell ref="AD37:AE37"/>
-    <mergeCell ref="N48:AA51"/>
-    <mergeCell ref="AB48:AD51"/>
-    <mergeCell ref="AE48:AE51"/>
-    <mergeCell ref="N52:AA54"/>
-    <mergeCell ref="AB52:AD54"/>
-    <mergeCell ref="AE52:AE54"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="T57:Z64"/>
-    <mergeCell ref="A65:AE65"/>
-    <mergeCell ref="T55:Z56"/>
-    <mergeCell ref="AA55:AD56"/>
-    <mergeCell ref="AE55:AE56"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="AA57:AD64"/>
-    <mergeCell ref="AE57:AE64"/>
-    <mergeCell ref="Q25:X25"/>
-    <mergeCell ref="Y25:AC25"/>
-    <mergeCell ref="Q26:X26"/>
-    <mergeCell ref="Y26:AC26"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="Q27:X27"/>
-    <mergeCell ref="Y27:AC27"/>
-    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="Q29:X29"/>
+    <mergeCell ref="Y29:AC29"/>
+    <mergeCell ref="AD29:AE29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:X38"/>
+    <mergeCell ref="Y38:AC38"/>
+    <mergeCell ref="AD38:AE38"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="Q24:X24"/>
@@ -11735,18 +12031,45 @@
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="H27:I27"/>
     <mergeCell ref="O27:P27"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="Q29:X29"/>
-    <mergeCell ref="Y29:AC29"/>
-    <mergeCell ref="AD29:AE29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="AD30:AE30"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:X38"/>
-    <mergeCell ref="Y38:AC38"/>
-    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="AB48:AD51"/>
+    <mergeCell ref="AE48:AE51"/>
+    <mergeCell ref="N52:AA54"/>
+    <mergeCell ref="AB52:AD54"/>
+    <mergeCell ref="AE52:AE54"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="T57:Z64"/>
+    <mergeCell ref="A65:AE65"/>
+    <mergeCell ref="T55:Z56"/>
+    <mergeCell ref="AA55:AD56"/>
+    <mergeCell ref="AE55:AE56"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="AA57:AD64"/>
+    <mergeCell ref="AE57:AE64"/>
+    <mergeCell ref="Y34:AC34"/>
+    <mergeCell ref="AD34:AE34"/>
+    <mergeCell ref="Y35:AC35"/>
+    <mergeCell ref="AD35:AE35"/>
+    <mergeCell ref="Q35:X35"/>
+    <mergeCell ref="Q36:X36"/>
+    <mergeCell ref="Y36:AC36"/>
+    <mergeCell ref="AD36:AE36"/>
+    <mergeCell ref="Q37:X37"/>
+    <mergeCell ref="Y37:AC37"/>
+    <mergeCell ref="AD37:AE37"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="N57:P64"/>
+    <mergeCell ref="Q57:S64"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="Q34:X34"/>
+    <mergeCell ref="N48:AA51"/>
     <mergeCell ref="N41:AE41"/>
     <mergeCell ref="N42:AA43"/>
     <mergeCell ref="AB42:AD43"/>
@@ -11754,10 +12077,104 @@
     <mergeCell ref="N44:AA47"/>
     <mergeCell ref="AB44:AD47"/>
     <mergeCell ref="AE44:AE47"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="Y23:AC23"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q32:X32"/>
+    <mergeCell ref="Q33:X33"/>
+    <mergeCell ref="Y33:AC33"/>
+    <mergeCell ref="AD33:AE33"/>
+    <mergeCell ref="Q30:X30"/>
+    <mergeCell ref="Y30:AC30"/>
+    <mergeCell ref="Q31:X31"/>
+    <mergeCell ref="Y31:AC31"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="Y32:AC32"/>
+    <mergeCell ref="AD32:AE32"/>
+    <mergeCell ref="Q25:X25"/>
+    <mergeCell ref="Y25:AC25"/>
+    <mergeCell ref="Q26:X26"/>
+    <mergeCell ref="Y26:AC26"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="Q27:X27"/>
+    <mergeCell ref="Y27:AC27"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="Q23:X23"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:X18"/>
+    <mergeCell ref="Y18:AC18"/>
+    <mergeCell ref="AD18:AE18"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:X19"/>
+    <mergeCell ref="Y19:AC19"/>
+    <mergeCell ref="AD19:AE19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="J10:W10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:W11"/>
+    <mergeCell ref="K12:AC12"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="J13:AC15"/>
+    <mergeCell ref="A16:AE16"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="O17:AE17"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A13:I15"/>
+    <mergeCell ref="AE1:AE2"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="I2:W5"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="X6:AB6"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="J7:W8"/>
+    <mergeCell ref="J9:W9"/>
+    <mergeCell ref="Q20:X20"/>
+    <mergeCell ref="Y20:AC20"/>
+    <mergeCell ref="Q21:X21"/>
+    <mergeCell ref="Y21:AC21"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="Q22:X22"/>
+    <mergeCell ref="Y22:AC22"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="O22:P22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins bottom="0.0" footer="0.0" header="0.0" left="0.0" right="0.0" top="0.0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>

--- a/MuoiCu_Server/templates/Phieu_Sua_Chua.xlsx
+++ b/MuoiCu_Server/templates/Phieu_Sua_Chua.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">  Cửa Hàng Bán Xe và Dịch Vụ Do Honda Ủy Nhiệm (HEAD TRUNG TRANG)</t>
   </si>
   <si>
-    <t xml:space="preserve">  HEAD TRUNG TRANG # 49010. </t>
+    <t xml:space="preserve">  HEAD TRUNG TRANG #49010</t>
   </si>
   <si>
     <t>PHIẾU SỬA CHỮA</t>
@@ -368,7 +368,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -473,13 +473,18 @@
       <name val="Tahoma"/>
     </font>
     <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
       <b/>
       <sz val="14.0"/>
       <color rgb="FFFF0000"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="14.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -948,7 +953,7 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1131,7 +1136,7 @@
     <xf borderId="28" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1151,7 +1156,7 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="24" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1163,11 +1168,11 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="1" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
@@ -1545,15 +1550,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.5"/>
+    <col customWidth="1" min="1" max="1" width="9.13"/>
     <col customWidth="1" min="2" max="3" width="5.88"/>
     <col customWidth="1" min="4" max="4" width="13.88"/>
     <col customWidth="1" min="5" max="5" width="43.75"/>
     <col customWidth="1" min="6" max="6" width="10.38"/>
-    <col customWidth="1" min="7" max="7" width="10.63"/>
-    <col customWidth="1" min="8" max="8" width="13.88"/>
-    <col customWidth="1" min="9" max="9" width="12.88"/>
-    <col customWidth="1" min="10" max="10" width="12.13"/>
+    <col customWidth="1" min="7" max="7" width="12.5"/>
+    <col customWidth="1" min="8" max="8" width="15.25"/>
+    <col customWidth="1" min="9" max="9" width="14.5"/>
+    <col customWidth="1" min="10" max="10" width="15.0"/>
     <col customWidth="1" min="11" max="11" width="9.88"/>
     <col customWidth="1" min="12" max="12" width="23.5"/>
     <col customWidth="1" min="13" max="13" width="11.0"/>
@@ -1571,8 +1576,8 @@
     <col customWidth="1" min="25" max="27" width="6.25"/>
     <col customWidth="1" min="28" max="28" width="10.63"/>
     <col customWidth="1" min="29" max="29" width="9.88"/>
-    <col customWidth="1" min="30" max="30" width="10.25"/>
-    <col customWidth="1" min="31" max="31" width="25.5"/>
+    <col customWidth="1" min="30" max="30" width="15.13"/>
+    <col customWidth="1" min="31" max="31" width="30.25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
@@ -1927,7 +1932,7 @@
       <c r="AD11" s="51"/>
       <c r="AE11" s="45"/>
     </row>
-    <row r="12" ht="26.25" customHeight="1">
+    <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="26" t="s">
         <v>26</v>
       </c>
@@ -3551,224 +3556,224 @@
     </row>
   </sheetData>
   <mergeCells count="218">
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:X34"/>
+    <mergeCell ref="Y34:AA34"/>
+    <mergeCell ref="AB34:AC34"/>
+    <mergeCell ref="AD34:AE34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="Q35:X35"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="AB35:AC35"/>
+    <mergeCell ref="AD35:AE35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="Q36:X36"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="AB36:AC36"/>
+    <mergeCell ref="AD36:AE36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="Q37:X37"/>
     <mergeCell ref="Y37:AA37"/>
-    <mergeCell ref="Q37:X37"/>
+    <mergeCell ref="AB37:AC37"/>
     <mergeCell ref="AD37:AE37"/>
-    <mergeCell ref="AD35:AE35"/>
-    <mergeCell ref="AD36:AE36"/>
-    <mergeCell ref="Y34:AA34"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="Q35:X35"/>
-    <mergeCell ref="Q36:X36"/>
-    <mergeCell ref="AB35:AC35"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="AD34:AE34"/>
-    <mergeCell ref="Y36:AA36"/>
-    <mergeCell ref="AB34:AC34"/>
-    <mergeCell ref="Q34:X34"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="Q19:X19"/>
-    <mergeCell ref="O17:AE17"/>
-    <mergeCell ref="Q18:X18"/>
-    <mergeCell ref="AD19:AE19"/>
-    <mergeCell ref="AD18:AE18"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="AD39:AE39"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:X38"/>
+    <mergeCell ref="Y38:AA38"/>
+    <mergeCell ref="AB38:AC38"/>
+    <mergeCell ref="A39:L39"/>
+    <mergeCell ref="N43:AA46"/>
+    <mergeCell ref="AB43:AD46"/>
+    <mergeCell ref="AE43:AE46"/>
+    <mergeCell ref="G46:L46"/>
+    <mergeCell ref="AB47:AD50"/>
+    <mergeCell ref="AE47:AE50"/>
+    <mergeCell ref="G48:I49"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="N54:V54"/>
+    <mergeCell ref="N55:Q55"/>
+    <mergeCell ref="R55:V55"/>
+    <mergeCell ref="N56:Q61"/>
+    <mergeCell ref="R56:V61"/>
+    <mergeCell ref="W56:AA61"/>
+    <mergeCell ref="AB56:AD61"/>
+    <mergeCell ref="AE56:AE61"/>
+    <mergeCell ref="N47:AA50"/>
+    <mergeCell ref="N51:AA53"/>
+    <mergeCell ref="AB51:AD53"/>
+    <mergeCell ref="AE51:AE53"/>
+    <mergeCell ref="W54:AA55"/>
+    <mergeCell ref="AB54:AD55"/>
+    <mergeCell ref="AE54:AE55"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="A45:F46"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B48:F49"/>
+    <mergeCell ref="J48:L61"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="AB1:AE1"/>
+    <mergeCell ref="I2:W5"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="Y4:AD4"/>
+    <mergeCell ref="X6:AB6"/>
+    <mergeCell ref="AC6:AD6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="J7:W8"/>
+    <mergeCell ref="J9:W9"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="J10:W10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="J11:W11"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="K12:AC12"/>
     <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="A13:I15"/>
+    <mergeCell ref="J13:AB15"/>
+    <mergeCell ref="A16:AE16"/>
     <mergeCell ref="Y18:AA18"/>
+    <mergeCell ref="AB18:AC18"/>
     <mergeCell ref="Y19:AA19"/>
     <mergeCell ref="AB19:AC19"/>
-    <mergeCell ref="AB18:AC18"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AB20:AC20"/>
-    <mergeCell ref="Q26:X26"/>
-    <mergeCell ref="Q27:X27"/>
-    <mergeCell ref="Q31:X31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q33:X33"/>
-    <mergeCell ref="Q30:X30"/>
-    <mergeCell ref="Q29:X29"/>
-    <mergeCell ref="Q32:X32"/>
-    <mergeCell ref="Y25:AA25"/>
-    <mergeCell ref="AB25:AC25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="Q25:X25"/>
-    <mergeCell ref="Q24:X24"/>
-    <mergeCell ref="Q28:X28"/>
-    <mergeCell ref="AB37:AC37"/>
-    <mergeCell ref="AB36:AC36"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="AB56:AD61"/>
-    <mergeCell ref="AB54:AD55"/>
-    <mergeCell ref="AB47:AD50"/>
-    <mergeCell ref="AB43:AD46"/>
-    <mergeCell ref="AB51:AD53"/>
-    <mergeCell ref="Q38:X38"/>
-    <mergeCell ref="Y38:AA38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="AB38:AC38"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="AE56:AE61"/>
-    <mergeCell ref="AE54:AE55"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="W56:AA61"/>
-    <mergeCell ref="R56:V61"/>
-    <mergeCell ref="N56:Q61"/>
-    <mergeCell ref="N54:V54"/>
-    <mergeCell ref="W54:AA55"/>
-    <mergeCell ref="AE51:AE53"/>
-    <mergeCell ref="AE43:AE46"/>
-    <mergeCell ref="AE47:AE50"/>
-    <mergeCell ref="AE41:AE42"/>
-    <mergeCell ref="AB41:AD42"/>
-    <mergeCell ref="AD39:AE39"/>
-    <mergeCell ref="N55:Q55"/>
-    <mergeCell ref="R55:V55"/>
-    <mergeCell ref="N47:AA50"/>
-    <mergeCell ref="N51:AA53"/>
-    <mergeCell ref="N43:AA46"/>
-    <mergeCell ref="N41:AA42"/>
-    <mergeCell ref="N40:AE40"/>
-    <mergeCell ref="Y26:AA26"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AB23:AC23"/>
-    <mergeCell ref="Y23:AA23"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="AB26:AC26"/>
-    <mergeCell ref="AB24:AC24"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="AD28:AE28"/>
-    <mergeCell ref="AD29:AE29"/>
-    <mergeCell ref="AB1:AE1"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AC6:AD6"/>
-    <mergeCell ref="AB29:AC29"/>
-    <mergeCell ref="X6:AB6"/>
-    <mergeCell ref="AD30:AE30"/>
-    <mergeCell ref="AB30:AC30"/>
-    <mergeCell ref="Y27:AA27"/>
-    <mergeCell ref="Y28:AA28"/>
-    <mergeCell ref="AB28:AC28"/>
-    <mergeCell ref="AB27:AC27"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="Y30:AA30"/>
-    <mergeCell ref="Y29:AA29"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="AD19:AE19"/>
+    <mergeCell ref="A17:L17"/>
     <mergeCell ref="M17:N17"/>
+    <mergeCell ref="O17:AE17"/>
+    <mergeCell ref="G18:I18"/>
     <mergeCell ref="O18:P18"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="J48:L61"/>
-    <mergeCell ref="G48:I49"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="A39:L39"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="A42:E43"/>
-    <mergeCell ref="A45:F46"/>
-    <mergeCell ref="G42:L43"/>
-    <mergeCell ref="G46:L46"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B48:F49"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="AB33:AC33"/>
-    <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="Y31:AA31"/>
-    <mergeCell ref="Y32:AA32"/>
-    <mergeCell ref="Y33:AA33"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="AB31:AC31"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="AB32:AC32"/>
-    <mergeCell ref="A13:I15"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="K12:AC12"/>
-    <mergeCell ref="J13:AB15"/>
-    <mergeCell ref="A16:AE16"/>
-    <mergeCell ref="J11:W11"/>
-    <mergeCell ref="J9:W9"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="Q22:X22"/>
-    <mergeCell ref="Y22:AA22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="Y21:AA21"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AB21:AC21"/>
-    <mergeCell ref="Q20:X20"/>
-    <mergeCell ref="Q21:X21"/>
-    <mergeCell ref="Q23:X23"/>
-    <mergeCell ref="AB22:AC22"/>
-    <mergeCell ref="I2:W5"/>
-    <mergeCell ref="Y4:AD4"/>
-    <mergeCell ref="J10:W10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="Q18:X18"/>
+    <mergeCell ref="AD18:AE18"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:X19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="N40:AE40"/>
+    <mergeCell ref="N41:AA42"/>
+    <mergeCell ref="AB41:AD42"/>
+    <mergeCell ref="AE41:AE42"/>
+    <mergeCell ref="A42:E43"/>
+    <mergeCell ref="G42:L43"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:X20"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="AB20:AC20"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="B21:F21"/>
     <mergeCell ref="G21:I21"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J7:W8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:X21"/>
+    <mergeCell ref="Y21:AA21"/>
+    <mergeCell ref="AB21:AC21"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="Q22:X22"/>
+    <mergeCell ref="Y22:AA22"/>
+    <mergeCell ref="AB22:AC22"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="Q23:X23"/>
+    <mergeCell ref="Y23:AA23"/>
+    <mergeCell ref="AB23:AC23"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="Q24:X24"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="AB24:AC24"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:X25"/>
+    <mergeCell ref="Y25:AA25"/>
+    <mergeCell ref="AB25:AC25"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="Q26:X26"/>
+    <mergeCell ref="Y26:AA26"/>
+    <mergeCell ref="AB26:AC26"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="Q27:X27"/>
+    <mergeCell ref="Y27:AA27"/>
+    <mergeCell ref="AB27:AC27"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="Q28:X28"/>
+    <mergeCell ref="Y28:AA28"/>
+    <mergeCell ref="AB28:AC28"/>
+    <mergeCell ref="AD28:AE28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="Q29:X29"/>
+    <mergeCell ref="Y29:AA29"/>
+    <mergeCell ref="AB29:AC29"/>
+    <mergeCell ref="AD29:AE29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:X30"/>
+    <mergeCell ref="Y30:AA30"/>
+    <mergeCell ref="AB30:AC30"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:X31"/>
+    <mergeCell ref="Y31:AA31"/>
+    <mergeCell ref="AB31:AC31"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="Q32:X32"/>
+    <mergeCell ref="Y32:AA32"/>
+    <mergeCell ref="AB32:AC32"/>
+    <mergeCell ref="AD32:AE32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:X33"/>
+    <mergeCell ref="Y33:AA33"/>
+    <mergeCell ref="AB33:AC33"/>
+    <mergeCell ref="AD33:AE33"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.75"/>
@@ -3785,15 +3790,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.5"/>
+    <col customWidth="1" min="1" max="1" width="9.13"/>
     <col customWidth="1" min="2" max="3" width="5.88"/>
     <col customWidth="1" min="4" max="4" width="13.88"/>
     <col customWidth="1" min="5" max="5" width="43.75"/>
     <col customWidth="1" min="6" max="6" width="10.38"/>
-    <col customWidth="1" min="7" max="7" width="10.63"/>
-    <col customWidth="1" min="8" max="8" width="13.88"/>
-    <col customWidth="1" min="9" max="9" width="12.88"/>
-    <col customWidth="1" min="10" max="10" width="12.13"/>
+    <col customWidth="1" min="7" max="7" width="12.5"/>
+    <col customWidth="1" min="8" max="8" width="15.25"/>
+    <col customWidth="1" min="9" max="9" width="14.5"/>
+    <col customWidth="1" min="10" max="10" width="15.0"/>
     <col customWidth="1" min="11" max="11" width="9.88"/>
     <col customWidth="1" min="12" max="12" width="23.5"/>
     <col customWidth="1" min="13" max="13" width="11.0"/>
@@ -3811,8 +3816,8 @@
     <col customWidth="1" min="25" max="27" width="6.25"/>
     <col customWidth="1" min="28" max="28" width="10.63"/>
     <col customWidth="1" min="29" max="29" width="9.88"/>
-    <col customWidth="1" min="30" max="30" width="10.25"/>
-    <col customWidth="1" min="31" max="31" width="25.5"/>
+    <col customWidth="1" min="30" max="30" width="15.13"/>
+    <col customWidth="1" min="31" max="31" width="30.25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
@@ -4167,7 +4172,7 @@
       <c r="AD11" s="51"/>
       <c r="AE11" s="45"/>
     </row>
-    <row r="12" ht="26.25" customHeight="1">
+    <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="26" t="s">
         <v>26</v>
       </c>
@@ -6025,15 +6030,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.5"/>
+    <col customWidth="1" min="1" max="1" width="9.13"/>
     <col customWidth="1" min="2" max="3" width="5.88"/>
     <col customWidth="1" min="4" max="4" width="13.88"/>
     <col customWidth="1" min="5" max="5" width="43.75"/>
     <col customWidth="1" min="6" max="6" width="10.38"/>
-    <col customWidth="1" min="7" max="7" width="10.63"/>
-    <col customWidth="1" min="8" max="8" width="13.88"/>
-    <col customWidth="1" min="9" max="9" width="12.88"/>
-    <col customWidth="1" min="10" max="10" width="12.13"/>
+    <col customWidth="1" min="7" max="7" width="12.5"/>
+    <col customWidth="1" min="8" max="8" width="15.25"/>
+    <col customWidth="1" min="9" max="9" width="14.5"/>
+    <col customWidth="1" min="10" max="10" width="15.0"/>
     <col customWidth="1" min="11" max="11" width="9.88"/>
     <col customWidth="1" min="12" max="12" width="23.5"/>
     <col customWidth="1" min="13" max="13" width="11.0"/>
@@ -6051,8 +6056,8 @@
     <col customWidth="1" min="25" max="27" width="6.25"/>
     <col customWidth="1" min="28" max="28" width="10.63"/>
     <col customWidth="1" min="29" max="29" width="9.88"/>
-    <col customWidth="1" min="30" max="30" width="10.25"/>
-    <col customWidth="1" min="31" max="31" width="25.5"/>
+    <col customWidth="1" min="30" max="30" width="15.13"/>
+    <col customWidth="1" min="31" max="31" width="30.25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
@@ -6407,7 +6412,7 @@
       <c r="AD11" s="51"/>
       <c r="AE11" s="45"/>
     </row>
-    <row r="12" ht="26.25" customHeight="1">
+    <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="26" t="s">
         <v>26</v>
       </c>
@@ -8265,15 +8270,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.5"/>
+    <col customWidth="1" min="1" max="1" width="9.13"/>
     <col customWidth="1" min="2" max="3" width="5.88"/>
     <col customWidth="1" min="4" max="4" width="13.88"/>
     <col customWidth="1" min="5" max="5" width="43.75"/>
     <col customWidth="1" min="6" max="6" width="10.38"/>
-    <col customWidth="1" min="7" max="7" width="10.63"/>
-    <col customWidth="1" min="8" max="8" width="13.88"/>
-    <col customWidth="1" min="9" max="9" width="12.88"/>
-    <col customWidth="1" min="10" max="10" width="12.13"/>
+    <col customWidth="1" min="7" max="7" width="12.5"/>
+    <col customWidth="1" min="8" max="8" width="15.25"/>
+    <col customWidth="1" min="9" max="9" width="14.5"/>
+    <col customWidth="1" min="10" max="10" width="15.0"/>
     <col customWidth="1" min="11" max="11" width="9.88"/>
     <col customWidth="1" min="12" max="12" width="23.5"/>
     <col customWidth="1" min="13" max="13" width="11.0"/>
@@ -8291,8 +8296,8 @@
     <col customWidth="1" min="25" max="27" width="6.25"/>
     <col customWidth="1" min="28" max="28" width="10.63"/>
     <col customWidth="1" min="29" max="29" width="9.88"/>
-    <col customWidth="1" min="30" max="30" width="10.25"/>
-    <col customWidth="1" min="31" max="31" width="25.5"/>
+    <col customWidth="1" min="30" max="30" width="15.13"/>
+    <col customWidth="1" min="31" max="31" width="30.25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
@@ -8647,7 +8652,7 @@
       <c r="AD11" s="51"/>
       <c r="AE11" s="45"/>
     </row>
-    <row r="12" ht="26.25" customHeight="1">
+    <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="26" t="s">
         <v>26</v>
       </c>
@@ -10505,15 +10510,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.5"/>
+    <col customWidth="1" min="1" max="1" width="9.13"/>
     <col customWidth="1" min="2" max="3" width="5.88"/>
     <col customWidth="1" min="4" max="4" width="13.88"/>
     <col customWidth="1" min="5" max="5" width="43.75"/>
     <col customWidth="1" min="6" max="6" width="10.38"/>
-    <col customWidth="1" min="7" max="7" width="10.63"/>
-    <col customWidth="1" min="8" max="8" width="13.88"/>
-    <col customWidth="1" min="9" max="9" width="12.88"/>
-    <col customWidth="1" min="10" max="10" width="12.13"/>
+    <col customWidth="1" min="7" max="7" width="12.5"/>
+    <col customWidth="1" min="8" max="8" width="15.25"/>
+    <col customWidth="1" min="9" max="9" width="14.5"/>
+    <col customWidth="1" min="10" max="10" width="15.0"/>
     <col customWidth="1" min="11" max="11" width="9.88"/>
     <col customWidth="1" min="12" max="12" width="23.5"/>
     <col customWidth="1" min="13" max="13" width="11.0"/>
@@ -10531,8 +10536,8 @@
     <col customWidth="1" min="25" max="27" width="6.25"/>
     <col customWidth="1" min="28" max="28" width="10.63"/>
     <col customWidth="1" min="29" max="29" width="9.88"/>
-    <col customWidth="1" min="30" max="30" width="10.25"/>
-    <col customWidth="1" min="31" max="31" width="25.5"/>
+    <col customWidth="1" min="30" max="30" width="15.13"/>
+    <col customWidth="1" min="31" max="31" width="30.25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
@@ -10887,7 +10892,7 @@
       <c r="AD11" s="51"/>
       <c r="AE11" s="45"/>
     </row>
-    <row r="12" ht="26.25" customHeight="1">
+    <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="26" t="s">
         <v>26</v>
       </c>
@@ -12511,6 +12516,29 @@
     </row>
   </sheetData>
   <mergeCells count="218">
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="AB51:AD53"/>
+    <mergeCell ref="AE51:AE53"/>
+    <mergeCell ref="N51:AA53"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="J48:L61"/>
+    <mergeCell ref="G48:I49"/>
+    <mergeCell ref="G46:L46"/>
+    <mergeCell ref="AB47:AD50"/>
+    <mergeCell ref="AB43:AD46"/>
+    <mergeCell ref="N43:AA46"/>
+    <mergeCell ref="N40:AE40"/>
+    <mergeCell ref="Y38:AA38"/>
+    <mergeCell ref="Y37:AA37"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="G37:I37"/>
     <mergeCell ref="W56:AA61"/>
     <mergeCell ref="W54:AA55"/>
     <mergeCell ref="N54:V54"/>
@@ -12518,217 +12546,194 @@
     <mergeCell ref="R56:V61"/>
     <mergeCell ref="N56:Q61"/>
     <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="AB54:AD55"/>
-    <mergeCell ref="AB51:AD53"/>
-    <mergeCell ref="AE51:AE53"/>
-    <mergeCell ref="AE54:AE55"/>
-    <mergeCell ref="N51:AA53"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="AB56:AD61"/>
-    <mergeCell ref="AE56:AE61"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="A39:L39"/>
     <mergeCell ref="R55:V55"/>
     <mergeCell ref="N55:Q55"/>
-    <mergeCell ref="AE41:AE42"/>
     <mergeCell ref="N41:AA42"/>
     <mergeCell ref="G42:L43"/>
     <mergeCell ref="A42:E43"/>
-    <mergeCell ref="AB41:AD42"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B58:F58"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B48:F49"/>
-    <mergeCell ref="AB47:AD50"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="J48:L61"/>
-    <mergeCell ref="G48:I49"/>
-    <mergeCell ref="G46:L46"/>
     <mergeCell ref="A45:F46"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:X38"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="AD37:AE37"/>
-    <mergeCell ref="AB37:AC37"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="A39:L39"/>
-    <mergeCell ref="Y27:AA27"/>
-    <mergeCell ref="Y28:AA28"/>
+    <mergeCell ref="N47:AA50"/>
+    <mergeCell ref="AB29:AC29"/>
+    <mergeCell ref="AB30:AC30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="Y30:AA30"/>
+    <mergeCell ref="Y29:AA29"/>
+    <mergeCell ref="AD28:AE28"/>
+    <mergeCell ref="Y32:AA32"/>
+    <mergeCell ref="Q32:X32"/>
+    <mergeCell ref="Q37:X37"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="Y33:AA33"/>
     <mergeCell ref="Y31:AA31"/>
-    <mergeCell ref="Y32:AA32"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="Y34:AA34"/>
+    <mergeCell ref="AB38:AC38"/>
+    <mergeCell ref="AB34:AC34"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="J11:W11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="J9:W9"/>
+    <mergeCell ref="J10:W10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="I2:W5"/>
+    <mergeCell ref="J7:W8"/>
+    <mergeCell ref="AB22:AC22"/>
+    <mergeCell ref="AB23:AC23"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AB21:AC21"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AB20:AC20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="AB19:AC19"/>
+    <mergeCell ref="Y4:AD4"/>
+    <mergeCell ref="AC6:AD6"/>
+    <mergeCell ref="X6:AB6"/>
+    <mergeCell ref="AD19:AE19"/>
+    <mergeCell ref="AD18:AE18"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="O17:AE17"/>
+    <mergeCell ref="A13:I15"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="K12:AC12"/>
+    <mergeCell ref="J13:AB15"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="A16:AE16"/>
+    <mergeCell ref="AB26:AC26"/>
+    <mergeCell ref="AB28:AC28"/>
+    <mergeCell ref="AB27:AC27"/>
+    <mergeCell ref="AB1:AE1"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="AD25:AE25"/>
     <mergeCell ref="AD26:AE26"/>
     <mergeCell ref="AD27:AE27"/>
     <mergeCell ref="AB25:AC25"/>
     <mergeCell ref="AB24:AC24"/>
     <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="AB31:AC31"/>
     <mergeCell ref="AD29:AE29"/>
     <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="AB36:AC36"/>
+    <mergeCell ref="AD36:AE36"/>
+    <mergeCell ref="AB31:AC31"/>
     <mergeCell ref="AB33:AC33"/>
     <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="Q23:X23"/>
-    <mergeCell ref="Y23:AA23"/>
-    <mergeCell ref="Y21:AA21"/>
-    <mergeCell ref="Q21:X21"/>
-    <mergeCell ref="Y18:AA18"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="AB18:AC18"/>
-    <mergeCell ref="Q24:X24"/>
-    <mergeCell ref="O17:AE17"/>
-    <mergeCell ref="Y26:AA26"/>
-    <mergeCell ref="AB26:AC26"/>
-    <mergeCell ref="AB28:AC28"/>
-    <mergeCell ref="AB27:AC27"/>
-    <mergeCell ref="AB29:AC29"/>
-    <mergeCell ref="AB30:AC30"/>
-    <mergeCell ref="Y19:AA19"/>
-    <mergeCell ref="AB19:AC19"/>
-    <mergeCell ref="Q32:X32"/>
-    <mergeCell ref="O32:P32"/>
     <mergeCell ref="AD32:AE32"/>
     <mergeCell ref="AB32:AC32"/>
     <mergeCell ref="AD35:AE35"/>
     <mergeCell ref="AB35:AC35"/>
-    <mergeCell ref="AB36:AC36"/>
-    <mergeCell ref="AD36:AE36"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="Y34:AA34"/>
+    <mergeCell ref="AD34:AE34"/>
+    <mergeCell ref="Y28:AA28"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:X38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="Y27:AA27"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="Q33:X33"/>
+    <mergeCell ref="Q34:X34"/>
     <mergeCell ref="Q35:X35"/>
     <mergeCell ref="Q36:X36"/>
-    <mergeCell ref="Q33:X33"/>
-    <mergeCell ref="Y36:AA36"/>
-    <mergeCell ref="Q34:X34"/>
-    <mergeCell ref="Y20:AA20"/>
-    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="Y26:AA26"/>
     <mergeCell ref="O26:P26"/>
+    <mergeCell ref="Q26:X26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="Y25:AA25"/>
     <mergeCell ref="O27:P27"/>
     <mergeCell ref="Q28:X28"/>
     <mergeCell ref="O28:P28"/>
-    <mergeCell ref="Q26:X26"/>
     <mergeCell ref="Q27:X27"/>
     <mergeCell ref="Q30:X30"/>
     <mergeCell ref="Q31:X31"/>
     <mergeCell ref="O31:P31"/>
     <mergeCell ref="O30:P30"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="Q29:X29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="AB56:AD61"/>
+    <mergeCell ref="AE56:AE61"/>
+    <mergeCell ref="AE47:AE50"/>
+    <mergeCell ref="AE43:AE46"/>
+    <mergeCell ref="AB54:AD55"/>
+    <mergeCell ref="AE54:AE55"/>
+    <mergeCell ref="AE41:AE42"/>
+    <mergeCell ref="AB41:AD42"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="AD37:AE37"/>
+    <mergeCell ref="AB37:AC37"/>
+    <mergeCell ref="AD39:AE39"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B48:F49"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="G32:I32"/>
     <mergeCell ref="B31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="Q29:X29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="A13:I15"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="Y18:AA18"/>
     <mergeCell ref="Q18:X18"/>
     <mergeCell ref="O18:P18"/>
-    <mergeCell ref="J9:W9"/>
-    <mergeCell ref="K12:AC12"/>
-    <mergeCell ref="J13:AB15"/>
-    <mergeCell ref="J11:W11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="Y4:AD4"/>
-    <mergeCell ref="AB1:AE1"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AC6:AD6"/>
-    <mergeCell ref="J10:W10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:I7"/>
-    <mergeCell ref="X6:AB6"/>
-    <mergeCell ref="I2:W5"/>
-    <mergeCell ref="J7:W8"/>
-    <mergeCell ref="AB43:AD46"/>
-    <mergeCell ref="N43:AA46"/>
-    <mergeCell ref="Y38:AA38"/>
-    <mergeCell ref="Y37:AA37"/>
-    <mergeCell ref="AE47:AE50"/>
-    <mergeCell ref="N47:AA50"/>
-    <mergeCell ref="AE43:AE46"/>
-    <mergeCell ref="AB38:AC38"/>
-    <mergeCell ref="AD39:AE39"/>
-    <mergeCell ref="N40:AE40"/>
-    <mergeCell ref="AD34:AE34"/>
-    <mergeCell ref="Q37:X37"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="AB22:AC22"/>
-    <mergeCell ref="AB23:AC23"/>
-    <mergeCell ref="AD19:AE19"/>
-    <mergeCell ref="AD18:AE18"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AB21:AC21"/>
-    <mergeCell ref="AB20:AC20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O21:P21"/>
     <mergeCell ref="Q22:X22"/>
     <mergeCell ref="Y22:AA22"/>
-    <mergeCell ref="Q20:X20"/>
+    <mergeCell ref="Q24:X24"/>
     <mergeCell ref="Q25:X25"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="A16:AE16"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="Q19:X19"/>
     <mergeCell ref="O24:P24"/>
     <mergeCell ref="O25:P25"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="Y30:AA30"/>
-    <mergeCell ref="Y29:AA29"/>
-    <mergeCell ref="Y33:AA33"/>
-    <mergeCell ref="AB34:AC34"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="Y25:AA25"/>
-    <mergeCell ref="AD28:AE28"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:X19"/>
+    <mergeCell ref="Q23:X23"/>
+    <mergeCell ref="Y23:AA23"/>
+    <mergeCell ref="Y21:AA21"/>
+    <mergeCell ref="Q21:X21"/>
+    <mergeCell ref="AB18:AC18"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="Q20:X20"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.75"/>
